--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>6536807</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>14.4280004501343</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>14.1920003890991</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>14.4280004501343</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>5113311</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>14.0380001068115</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>14.1879997253418</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>5044380</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>14.3780002593994</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>14.1879997253418</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>14.2559995651245</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>14.3100004196167</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>6074983</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>14.5579996109009</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>14.3420000076294</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>14.3760004043579</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>14.4540004730225</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>4143682</v>
+        <v>2946112</v>
       </c>
       <c r="C2715" t="n">
-        <v>14.423999786377</v>
+        <v>14.3179998397827</v>
       </c>
       <c r="D2715" t="n">
-        <v>14.1719999313354</v>
+        <v>14.1300001144409</v>
       </c>
       <c r="E2715" t="n">
-        <v>14.2559995651245</v>
+        <v>14.3159999847412</v>
       </c>
       <c r="F2715" t="n">
-        <v>14.4099998474121</v>
+        <v>14.3179998397827</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>6253572</v>
+        <v>4143682</v>
       </c>
       <c r="C2716" t="n">
-        <v>14.3559999465942</v>
+        <v>14.423999786377</v>
       </c>
       <c r="D2716" t="n">
-        <v>13.9820003509521</v>
+        <v>14.1719999313354</v>
       </c>
       <c r="E2716" t="n">
-        <v>14.253999710083</v>
+        <v>14.2559995651245</v>
       </c>
       <c r="F2716" t="n">
-        <v>14.3559999465942</v>
+        <v>14.4099998474121</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>4955815</v>
+        <v>6253572</v>
       </c>
       <c r="C2717" t="n">
-        <v>14.4479999542236</v>
+        <v>14.3559999465942</v>
       </c>
       <c r="D2717" t="n">
-        <v>14.039999961853</v>
+        <v>13.9820003509521</v>
       </c>
       <c r="E2717" t="n">
-        <v>14.3760004043579</v>
+        <v>14.253999710083</v>
       </c>
       <c r="F2717" t="n">
-        <v>14.1879997253418</v>
+        <v>14.3559999465942</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>4874209</v>
+        <v>4955815</v>
       </c>
       <c r="C2718" t="n">
-        <v>14.3680000305176</v>
+        <v>14.4479999542236</v>
       </c>
       <c r="D2718" t="n">
-        <v>14.1899995803833</v>
+        <v>14.039999961853</v>
       </c>
       <c r="E2718" t="n">
-        <v>14.2519998550415</v>
+        <v>14.3760004043579</v>
       </c>
       <c r="F2718" t="n">
-        <v>14.3559999465942</v>
+        <v>14.1879997253418</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>6536807</v>
+        <v>4874209</v>
       </c>
       <c r="C2719" t="n">
-        <v>14.4280004501343</v>
+        <v>14.3680000305176</v>
       </c>
       <c r="D2719" t="n">
-        <v>14.1920003890991</v>
+        <v>14.1899995803833</v>
       </c>
       <c r="E2719" t="n">
-        <v>14.25</v>
+        <v>14.2519998550415</v>
       </c>
       <c r="F2719" t="n">
-        <v>14.4280004501343</v>
+        <v>14.3559999465942</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>5113311</v>
+        <v>6536807</v>
       </c>
       <c r="C2720" t="n">
-        <v>14.3000001907349</v>
+        <v>14.4280004501343</v>
       </c>
       <c r="D2720" t="n">
-        <v>14.0380001068115</v>
+        <v>14.1920003890991</v>
       </c>
       <c r="E2720" t="n">
-        <v>14.3000001907349</v>
+        <v>14.25</v>
       </c>
       <c r="F2720" t="n">
-        <v>14.1879997253418</v>
+        <v>14.4280004501343</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>5044380</v>
+        <v>5113311</v>
       </c>
       <c r="C2721" t="n">
-        <v>14.3780002593994</v>
+        <v>14.3000001907349</v>
       </c>
       <c r="D2721" t="n">
+        <v>14.0380001068115</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="F2721" t="n">
         <v>14.1879997253418</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>14.2559995651245</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>14.3100004196167</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>6074983</v>
+        <v>5044380</v>
       </c>
       <c r="C2722" t="n">
-        <v>14.5579996109009</v>
+        <v>14.3780002593994</v>
       </c>
       <c r="D2722" t="n">
-        <v>14.3420000076294</v>
+        <v>14.1879997253418</v>
       </c>
       <c r="E2722" t="n">
-        <v>14.3760004043579</v>
+        <v>14.2559995651245</v>
       </c>
       <c r="F2722" t="n">
-        <v>14.4540004730225</v>
+        <v>14.3100004196167</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>10856597</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>14.1199998855591</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>14.4479999542236</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>14.2019996643066</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>13.5500001907349</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>13.8159999847412</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>5321445</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>14.0699996948242</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>13.8760004043579</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>13.8900003433228</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>13.8900003433228</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>14.0279998779297</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>6902114</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>13.9779996871948</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>13.4040002822876</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>13.8999996185303</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>13.5100002288818</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>6537751</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>13.4079999923706</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>13.0880002975464</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>13.1499996185303</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>13.1499996185303</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>13.2119998931885</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>4987316</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>13.5159997940063</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>13.293999671936</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>13.3120002746582</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>5173468</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>13.673999786377</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>13.3680000305176</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>13.3680000305176</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>13.5839996337891</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.58926391601562</v>
       </c>
       <c r="G2" t="n">
-        <v>3.21858596801758</v>
+        <v>3.218585729599</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.44035005569458</v>
       </c>
       <c r="G4" t="n">
-        <v>3.11414837837219</v>
+        <v>3.11414813995361</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.24405384063721</v>
       </c>
       <c r="G7" t="n">
-        <v>2.97647976875305</v>
+        <v>2.97648000717163</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.21020889282227</v>
       </c>
       <c r="G8" t="n">
-        <v>2.95274353027344</v>
+        <v>2.95274329185486</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.41327381134033</v>
       </c>
       <c r="G10" t="n">
-        <v>3.09515881538391</v>
+        <v>3.09515905380249</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.18651914596558</v>
       </c>
       <c r="G11" t="n">
-        <v>2.93612933158875</v>
+        <v>2.93612957000732</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.82100200653076</v>
       </c>
       <c r="G12" t="n">
-        <v>2.67978096008301</v>
+        <v>2.67978143692017</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.80408000946045</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66791319847107</v>
+        <v>2.66791367530823</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.52655792236328</v>
       </c>
       <c r="G14" t="n">
-        <v>2.47327876091003</v>
+        <v>2.47327923774719</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.77023601531982</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64417767524719</v>
+        <v>2.64417791366577</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.82777094841003</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68452835083008</v>
+        <v>2.68452882766724</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.54009604454041</v>
       </c>
       <c r="G20" t="n">
-        <v>2.48277378082275</v>
+        <v>2.48277354240417</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.38441300392151</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3735888004303</v>
+        <v>2.37358856201172</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.11636710166931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18560004234314</v>
+        <v>2.18559980392456</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.05138611793518</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14002680778503</v>
+        <v>2.14002704620361</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.6872239112854</v>
       </c>
       <c r="G27" t="n">
-        <v>1.88462948799133</v>
+        <v>1.88462924957275</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.62901210784912</v>
       </c>
       <c r="G28" t="n">
-        <v>1.84380352497101</v>
+        <v>1.84380388259888</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.83343005180359</v>
       </c>
       <c r="G31" t="n">
-        <v>1.98716771602631</v>
+        <v>1.98716795444489</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.35056900978088</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34985303878784</v>
+        <v>2.34985280036926</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.13125896453857</v>
       </c>
       <c r="G36" t="n">
-        <v>2.19604420661926</v>
+        <v>2.19604396820068</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.44871711730957</v>
       </c>
       <c r="G37" t="n">
-        <v>2.41868734359741</v>
+        <v>2.41868710517883</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.31807804107666</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32706594467163</v>
+        <v>2.32706570625305</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.18405508995056</v>
       </c>
       <c r="G40" t="n">
-        <v>2.23307132720947</v>
+        <v>2.23307156562805</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.18811702728271</v>
       </c>
       <c r="G42" t="n">
-        <v>2.23592066764832</v>
+        <v>2.23592042922974</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.23549795150757</v>
       </c>
       <c r="G43" t="n">
-        <v>2.26914978027344</v>
+        <v>2.26915001869202</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.33567690849304</v>
       </c>
       <c r="G45" t="n">
-        <v>2.33940839767456</v>
+        <v>2.33940863609314</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.17593288421631</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22737526893616</v>
+        <v>2.22737503051758</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.12990498542786</v>
       </c>
       <c r="G48" t="n">
-        <v>2.19509434700012</v>
+        <v>2.1950945854187</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G49" t="n">
-        <v>2.21977972984314</v>
+        <v>2.2197802066803</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.39118099212646</v>
       </c>
       <c r="G53" t="n">
-        <v>2.37833499908447</v>
+        <v>2.37833523750305</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.38441300392151</v>
       </c>
       <c r="G54" t="n">
-        <v>2.3735888004303</v>
+        <v>2.37358856201172</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.16104102134705</v>
       </c>
       <c r="G55" t="n">
-        <v>2.21693110466003</v>
+        <v>2.21693158149719</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.21654605865479</v>
       </c>
       <c r="G58" t="n">
-        <v>2.25585865974426</v>
+        <v>2.25585889816284</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.16916394233704</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22262811660767</v>
+        <v>2.22262835502625</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.95526909828186</v>
       </c>
       <c r="G61" t="n">
-        <v>2.0726170539856</v>
+        <v>2.07261753082275</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.92548608779907</v>
       </c>
       <c r="G62" t="n">
-        <v>2.05172944068909</v>
+        <v>2.05172967910767</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.83343005180359</v>
       </c>
       <c r="G64" t="n">
-        <v>1.98716771602631</v>
+        <v>1.98716795444489</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.54507803916931</v>
       </c>
       <c r="G68" t="n">
-        <v>1.78493821620941</v>
+        <v>1.7849383354187</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.92819404602051</v>
       </c>
       <c r="G71" t="n">
-        <v>2.05362868309021</v>
+        <v>2.05362892150879</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.26392793655396</v>
       </c>
       <c r="G72" t="n">
-        <v>2.28908920288086</v>
+        <v>2.28908848762512</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.33567690849304</v>
       </c>
       <c r="G74" t="n">
-        <v>2.33940839767456</v>
+        <v>2.33940863609314</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.4216411113739</v>
       </c>
       <c r="G75" t="n">
-        <v>2.39969778060913</v>
+        <v>2.39969754219055</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.30724811553955</v>
       </c>
       <c r="G76" t="n">
-        <v>2.31947088241577</v>
+        <v>2.31947040557861</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.40471911430359</v>
       </c>
       <c r="G77" t="n">
-        <v>2.38782954216003</v>
+        <v>2.38782978057861</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.51302003860474</v>
       </c>
       <c r="G78" t="n">
-        <v>2.46378397941589</v>
+        <v>2.46378445625305</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.40810394287109</v>
       </c>
       <c r="G80" t="n">
-        <v>2.39020371437073</v>
+        <v>2.39020347595215</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.46563911437988</v>
       </c>
       <c r="G82" t="n">
-        <v>2.43055510520935</v>
+        <v>2.43055462837219</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.60101509094238</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52549815177917</v>
+        <v>2.5254979133606</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.32890796661377</v>
       </c>
       <c r="G85" t="n">
-        <v>2.33466124534607</v>
+        <v>2.33466100692749</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.18270206451416</v>
       </c>
       <c r="G86" t="n">
-        <v>2.23212289810181</v>
+        <v>2.23212265968323</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.05950903892517</v>
       </c>
       <c r="G88" t="n">
-        <v>2.14572381973267</v>
+        <v>2.14572358131409</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.9579770565033</v>
       </c>
       <c r="G95" t="n">
-        <v>2.07451605796814</v>
+        <v>2.07451629638672</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.97557592391968</v>
       </c>
       <c r="G98" t="n">
-        <v>2.08685922622681</v>
+        <v>2.08685898780823</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88758111000061</v>
       </c>
       <c r="G100" t="n">
-        <v>2.07167911529541</v>
+        <v>2.07167887687683</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.27069592475891</v>
       </c>
       <c r="G102" t="n">
-        <v>2.34654307365417</v>
+        <v>2.3465428352356</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.2070689201355</v>
       </c>
       <c r="G103" t="n">
-        <v>2.30089402198792</v>
+        <v>2.30089426040649</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.21519207954407</v>
       </c>
       <c r="G104" t="n">
-        <v>2.30672192573547</v>
+        <v>2.30672168731689</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.07846188545227</v>
       </c>
       <c r="G106" t="n">
-        <v>2.20862531661987</v>
+        <v>2.20862579345703</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94579291343689</v>
       </c>
       <c r="G107" t="n">
-        <v>2.11344265937805</v>
+        <v>2.11344289779663</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.99723601341248</v>
       </c>
       <c r="G113" t="n">
-        <v>2.15035033226013</v>
+        <v>2.15035057067871</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.63036489486694</v>
       </c>
       <c r="G115" t="n">
-        <v>1.88714075088501</v>
+        <v>1.88714051246643</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.55590796470642</v>
       </c>
       <c r="G116" t="n">
-        <v>1.83372223377228</v>
+        <v>1.83372187614441</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.54778599739075</v>
       </c>
       <c r="G117" t="n">
-        <v>1.82789492607117</v>
+        <v>1.82789516448975</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.4814510345459</v>
       </c>
       <c r="G118" t="n">
-        <v>1.78030335903168</v>
+        <v>1.78030347824097</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.72783708572388</v>
       </c>
       <c r="G119" t="n">
-        <v>1.95707190036774</v>
+        <v>1.95707166194916</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.85102891921997</v>
       </c>
       <c r="G120" t="n">
-        <v>2.04545497894287</v>
+        <v>2.04545521736145</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.91194891929626</v>
       </c>
       <c r="G122" t="n">
-        <v>2.08916187286377</v>
+        <v>2.08916163444519</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.13531994819641</v>
       </c>
       <c r="G123" t="n">
-        <v>2.24941802024841</v>
+        <v>2.24941778182983</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.36367392539978</v>
       </c>
       <c r="G124" t="n">
-        <v>1.69580483436584</v>
+        <v>1.69580495357513</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G125" t="n">
-        <v>1.67832207679749</v>
+        <v>1.67832243442535</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.159255027771</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54914557933807</v>
+        <v>1.54914569854736</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.21882104873657</v>
       </c>
       <c r="G128" t="n">
-        <v>1.59188079833984</v>
+        <v>1.59188091754913</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.11187291145325</v>
       </c>
       <c r="G129" t="n">
-        <v>1.51515161991119</v>
+        <v>1.5151515007019</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.83028995990753</v>
       </c>
       <c r="G132" t="n">
-        <v>1.31313157081604</v>
+        <v>1.31313133239746</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.74770998954773</v>
       </c>
       <c r="G133" t="n">
-        <v>1.25388491153717</v>
+        <v>1.25388503074646</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.03064703941345</v>
       </c>
       <c r="G134" t="n">
-        <v>1.45687651634216</v>
+        <v>1.45687675476074</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.12541103363037</v>
       </c>
       <c r="G135" t="n">
-        <v>1.52486455440521</v>
+        <v>1.52486431598663</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.18362307548523</v>
       </c>
       <c r="G137" t="n">
-        <v>1.56662845611572</v>
+        <v>1.56662821769714</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.27703309059143</v>
       </c>
       <c r="G138" t="n">
-        <v>1.63364481925964</v>
+        <v>1.63364493846893</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.31764602661133</v>
       </c>
       <c r="G140" t="n">
-        <v>1.66278219223022</v>
+        <v>1.66278266906738</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.29598498344421</v>
       </c>
       <c r="G141" t="n">
-        <v>1.64724171161652</v>
+        <v>1.64724159240723</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.32035303115845</v>
       </c>
       <c r="G142" t="n">
-        <v>1.66472470760345</v>
+        <v>1.66472446918488</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G143" t="n">
-        <v>1.71814346313477</v>
+        <v>1.7181431055069</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.37721109390259</v>
       </c>
       <c r="G144" t="n">
-        <v>1.70551693439484</v>
+        <v>1.70551729202271</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.32441401481628</v>
       </c>
       <c r="G146" t="n">
-        <v>1.66763818264008</v>
+        <v>1.6676379442215</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.43136191368103</v>
       </c>
       <c r="G147" t="n">
-        <v>1.74436724185944</v>
+        <v>1.74436736106873</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.34336709976196</v>
       </c>
       <c r="G150" t="n">
-        <v>1.68123590946198</v>
+        <v>1.6812356710434</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.05366110801697</v>
       </c>
       <c r="G151" t="n">
-        <v>1.47338771820068</v>
+        <v>1.47338783740997</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.14707088470459</v>
       </c>
       <c r="G153" t="n">
-        <v>1.54040431976318</v>
+        <v>1.5404040813446</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.42730093002319</v>
       </c>
       <c r="G154" t="n">
-        <v>1.7414538860321</v>
+        <v>1.74145364761353</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.38262605667114</v>
       </c>
       <c r="G155" t="n">
-        <v>1.70940184593201</v>
+        <v>1.70940208435059</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.41376304626465</v>
       </c>
       <c r="G158" t="n">
-        <v>1.73174095153809</v>
+        <v>1.73174107074738</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.36231994628906</v>
       </c>
       <c r="G160" t="n">
-        <v>1.69483351707458</v>
+        <v>1.6948333978653</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.27432489395142</v>
       </c>
       <c r="G161" t="n">
-        <v>1.63170182704926</v>
+        <v>1.63170206546783</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.31493806838989</v>
       </c>
       <c r="G162" t="n">
-        <v>1.66083943843842</v>
+        <v>1.66083955764771</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.18091511726379</v>
       </c>
       <c r="G163" t="n">
-        <v>1.56468546390533</v>
+        <v>1.56468558311462</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.19580698013306</v>
       </c>
       <c r="G164" t="n">
-        <v>1.57536971569061</v>
+        <v>1.57536959648132</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.32441401481628</v>
       </c>
       <c r="G168" t="n">
-        <v>1.66763818264008</v>
+        <v>1.6676379442215</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.31899905204773</v>
       </c>
       <c r="G170" t="n">
-        <v>1.66375327110291</v>
+        <v>1.66375315189362</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.33524489402771</v>
       </c>
       <c r="G171" t="n">
-        <v>1.67540860176086</v>
+        <v>1.67540848255157</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.41105508804321</v>
       </c>
       <c r="G173" t="n">
-        <v>1.72979831695557</v>
+        <v>1.72979819774628</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.41105508804321</v>
       </c>
       <c r="G174" t="n">
-        <v>1.72979831695557</v>
+        <v>1.72979819774628</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.36773490905762</v>
       </c>
       <c r="G175" t="n">
-        <v>1.69871830940247</v>
+        <v>1.69871866703033</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.44760704040527</v>
       </c>
       <c r="G176" t="n">
-        <v>1.75602233409882</v>
+        <v>1.75602197647095</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.45166802406311</v>
       </c>
       <c r="G177" t="n">
-        <v>1.75893592834473</v>
+        <v>1.75893568992615</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.40293288230896</v>
       </c>
       <c r="G178" t="n">
-        <v>1.72397077083588</v>
+        <v>1.72397112846375</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.35690498352051</v>
       </c>
       <c r="G179" t="n">
-        <v>1.69094860553741</v>
+        <v>1.69094836711884</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.29463195800781</v>
       </c>
       <c r="G180" t="n">
-        <v>1.6462709903717</v>
+        <v>1.64627087116241</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.29598498344421</v>
       </c>
       <c r="G182" t="n">
-        <v>1.64724171161652</v>
+        <v>1.64724159240723</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.21746706962585</v>
       </c>
       <c r="G183" t="n">
-        <v>1.59090936183929</v>
+        <v>1.59090971946716</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.25131106376648</v>
       </c>
       <c r="G184" t="n">
-        <v>1.61519074440002</v>
+        <v>1.61519086360931</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.15519404411316</v>
       </c>
       <c r="G185" t="n">
-        <v>1.54623186588287</v>
+        <v>1.54623210430145</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.25672602653503</v>
       </c>
       <c r="G186" t="n">
-        <v>1.61907577514648</v>
+        <v>1.61907553672791</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.26214098930359</v>
       </c>
       <c r="G187" t="n">
-        <v>1.62296068668365</v>
+        <v>1.62296056747437</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.19580698013306</v>
       </c>
       <c r="G188" t="n">
-        <v>1.57536971569061</v>
+        <v>1.57536959648132</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.12676501274109</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52583587169647</v>
+        <v>1.52583599090576</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.17820811271667</v>
       </c>
       <c r="G192" t="n">
-        <v>1.56274354457855</v>
+        <v>1.56274330615997</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.24183511734009</v>
       </c>
       <c r="G193" t="n">
-        <v>1.60839211940765</v>
+        <v>1.60839235782623</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.1903920173645</v>
       </c>
       <c r="G194" t="n">
-        <v>1.57148468494415</v>
+        <v>1.57148480415344</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.18362307548523</v>
       </c>
       <c r="G195" t="n">
-        <v>1.56662845611572</v>
+        <v>1.56662821769714</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.29327797889709</v>
       </c>
       <c r="G196" t="n">
-        <v>1.64529979228973</v>
+        <v>1.64529967308044</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.26755595207214</v>
       </c>
       <c r="G198" t="n">
-        <v>1.62684547901154</v>
+        <v>1.62684571743011</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.34878206253052</v>
       </c>
       <c r="G199" t="n">
-        <v>1.68512058258057</v>
+        <v>1.68512082099915</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.49092793464661</v>
       </c>
       <c r="G200" t="n">
-        <v>1.78710246086121</v>
+        <v>1.78710281848907</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.61682796478271</v>
       </c>
       <c r="G204" t="n">
-        <v>1.87742865085602</v>
+        <v>1.87742900848389</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.75085091590881</v>
       </c>
       <c r="G205" t="n">
-        <v>1.97358250617981</v>
+        <v>1.97358322143555</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.8753969669342</v>
       </c>
       <c r="G207" t="n">
-        <v>2.06293773651123</v>
+        <v>2.06293749809265</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.85102891921997</v>
       </c>
       <c r="G208" t="n">
-        <v>2.04545497894287</v>
+        <v>2.04545521736145</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.94849991798401</v>
       </c>
       <c r="G209" t="n">
-        <v>2.11538529396057</v>
+        <v>2.11538505554199</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.87133598327637</v>
       </c>
       <c r="G211" t="n">
-        <v>2.06002449989319</v>
+        <v>2.06002402305603</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.93902397155762</v>
       </c>
       <c r="G212" t="n">
-        <v>2.10858678817749</v>
+        <v>2.10858631134033</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.89299607276917</v>
       </c>
       <c r="G214" t="n">
-        <v>2.07556414604187</v>
+        <v>2.07556438446045</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.64390301704407</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89685344696045</v>
+        <v>1.89685356616974</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.82936906814575</v>
       </c>
       <c r="G223" t="n">
-        <v>2.02991557121277</v>
+        <v>2.02991533279419</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.79958605766296</v>
       </c>
       <c r="G224" t="n">
-        <v>2.00854754447937</v>
+        <v>2.00854778289795</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.58975195884705</v>
       </c>
       <c r="G227" t="n">
-        <v>1.85800325870514</v>
+        <v>1.85800337791443</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.53695607185364</v>
       </c>
       <c r="G228" t="n">
-        <v>1.82012522220612</v>
+        <v>1.82012510299683</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.52612495422363</v>
       </c>
       <c r="G229" t="n">
-        <v>1.81235456466675</v>
+        <v>1.81235444545746</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.57215309143066</v>
       </c>
       <c r="G233" t="n">
-        <v>1.84537708759308</v>
+        <v>1.8453768491745</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.40293288230896</v>
       </c>
       <c r="G234" t="n">
-        <v>1.72397077083588</v>
+        <v>1.72397112846375</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.53289389610291</v>
       </c>
       <c r="G235" t="n">
-        <v>1.81721091270447</v>
+        <v>1.81721103191376</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.56538510322571</v>
       </c>
       <c r="G236" t="n">
-        <v>1.84052097797394</v>
+        <v>1.84052121639252</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.20165395736694</v>
       </c>
       <c r="G241" t="n">
-        <v>2.29700922966003</v>
+        <v>2.29700899124146</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.19759297370911</v>
       </c>
       <c r="G243" t="n">
-        <v>2.29409503936768</v>
+        <v>2.29409551620483</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.25715899467468</v>
       </c>
       <c r="G244" t="n">
-        <v>2.33683085441589</v>
+        <v>2.33683109283447</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.27204990386963</v>
       </c>
       <c r="G246" t="n">
-        <v>2.34751391410828</v>
+        <v>2.34751439094543</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.36004495620728</v>
       </c>
       <c r="G247" t="n">
-        <v>2.41064596176147</v>
+        <v>2.4106457233429</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.25715899467468</v>
       </c>
       <c r="G249" t="n">
-        <v>2.33683085441589</v>
+        <v>2.33683109283447</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.36410593986511</v>
       </c>
       <c r="G250" t="n">
-        <v>2.4135594367981</v>
+        <v>2.41355919837952</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.45886993408203</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48154735565186</v>
+        <v>2.48154711723328</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.49271392822266</v>
       </c>
       <c r="G253" t="n">
-        <v>2.50582885742188</v>
+        <v>2.50582838058472</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.5028669834137</v>
       </c>
       <c r="G254" t="n">
-        <v>2.51311302185059</v>
+        <v>2.51311278343201</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.45886993408203</v>
       </c>
       <c r="G255" t="n">
-        <v>2.48154735565186</v>
+        <v>2.48154711723328</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.42502593994141</v>
       </c>
       <c r="G256" t="n">
-        <v>2.45726609230042</v>
+        <v>2.45726585388184</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.42502593994141</v>
       </c>
       <c r="G257" t="n">
-        <v>2.45726609230042</v>
+        <v>2.45726585388184</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.56717109680176</v>
       </c>
       <c r="G258" t="n">
-        <v>2.5592474937439</v>
+        <v>2.55924725532532</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.64162802696228</v>
       </c>
       <c r="G260" t="n">
-        <v>2.61266613006592</v>
+        <v>2.61266589164734</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.64162802696228</v>
       </c>
       <c r="G261" t="n">
-        <v>2.61266613006592</v>
+        <v>2.61266589164734</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.49271392822266</v>
       </c>
       <c r="G263" t="n">
-        <v>2.50582885742188</v>
+        <v>2.50582838058472</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.49271392822266</v>
       </c>
       <c r="G264" t="n">
-        <v>2.50582885742188</v>
+        <v>2.50582838058472</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.40810394287109</v>
       </c>
       <c r="G265" t="n">
-        <v>2.44512534141541</v>
+        <v>2.44512557983398</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.59424591064453</v>
       </c>
       <c r="G267" t="n">
-        <v>2.5786714553833</v>
+        <v>2.57867193222046</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.56040191650391</v>
       </c>
       <c r="G268" t="n">
-        <v>2.5543909072876</v>
+        <v>2.55439066886902</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.82777094841003</v>
       </c>
       <c r="G271" t="n">
-        <v>2.74621295928955</v>
+        <v>2.74621319770813</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.88868999481201</v>
       </c>
       <c r="G272" t="n">
-        <v>2.78991913795471</v>
+        <v>2.78991937637329</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.85484600067139</v>
       </c>
       <c r="G275" t="n">
-        <v>2.76563811302185</v>
+        <v>2.76563787460327</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.79392695426941</v>
       </c>
       <c r="G276" t="n">
-        <v>2.72193217277527</v>
+        <v>2.72193193435669</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.61455297470093</v>
       </c>
       <c r="G278" t="n">
-        <v>2.5932412147522</v>
+        <v>2.59324097633362</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.64501190185547</v>
       </c>
       <c r="G281" t="n">
-        <v>2.61509370803833</v>
+        <v>2.61509346961975</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.73300695419312</v>
       </c>
       <c r="G282" t="n">
-        <v>2.67822504043579</v>
+        <v>2.67822527885437</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.51978898048401</v>
       </c>
       <c r="G283" t="n">
-        <v>2.52525329589844</v>
+        <v>2.52525305747986</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.43856310844421</v>
       </c>
       <c r="G285" t="n">
-        <v>2.46697807312012</v>
+        <v>2.4669783115387</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.49271392822266</v>
       </c>
       <c r="G286" t="n">
-        <v>2.50582885742188</v>
+        <v>2.50582838058472</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.2192530632019</v>
       </c>
       <c r="G287" t="n">
-        <v>2.30963563919067</v>
+        <v>2.30963540077209</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.34109210968018</v>
       </c>
       <c r="G289" t="n">
-        <v>2.39704847335815</v>
+        <v>2.397047996521</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G291" t="n">
-        <v>2.25524568557739</v>
+        <v>2.25524544715881</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.04597091674805</v>
       </c>
       <c r="G292" t="n">
-        <v>2.18531489372253</v>
+        <v>2.18531513214111</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.03243398666382</v>
       </c>
       <c r="G300" t="n">
-        <v>2.17560291290283</v>
+        <v>2.17560267448425</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.18134808540344</v>
       </c>
       <c r="G302" t="n">
-        <v>2.28244042396545</v>
+        <v>2.28244066238403</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.96474504470825</v>
       </c>
       <c r="G304" t="n">
-        <v>2.12703967094421</v>
+        <v>2.12704014778137</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.97151398658752</v>
       </c>
       <c r="G305" t="n">
-        <v>2.13189649581909</v>
+        <v>2.13189601898193</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.11772108078003</v>
       </c>
       <c r="G308" t="n">
-        <v>2.23679184913635</v>
+        <v>2.23679161071777</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.03784894943237</v>
       </c>
       <c r="G309" t="n">
-        <v>2.17948818206787</v>
+        <v>2.17948794364929</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.15698003768921</v>
       </c>
       <c r="G313" t="n">
-        <v>2.26495838165283</v>
+        <v>2.26495814323425</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.25174403190613</v>
       </c>
       <c r="G314" t="n">
-        <v>2.33294582366943</v>
+        <v>2.33294606208801</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.26392793655396</v>
       </c>
       <c r="G315" t="n">
-        <v>2.34168744087219</v>
+        <v>2.34168720245361</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.31807804107666</v>
       </c>
       <c r="G317" t="n">
-        <v>2.38053679466248</v>
+        <v>2.3805365562439</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.25851202011108</v>
       </c>
       <c r="G318" t="n">
-        <v>2.33780169487</v>
+        <v>2.33780121803284</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.27881908416748</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35237097740173</v>
+        <v>2.352370262146</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.2179000377655</v>
       </c>
       <c r="G320" t="n">
-        <v>2.30866456031799</v>
+        <v>2.30866479873657</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.07710790634155</v>
       </c>
       <c r="G325" t="n">
-        <v>2.20765399932861</v>
+        <v>2.20765423774719</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.95256209373474</v>
       </c>
       <c r="G331" t="n">
-        <v>2.11829948425293</v>
+        <v>2.11829900741577</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.10282897949219</v>
       </c>
       <c r="G335" t="n">
-        <v>2.2261073589325</v>
+        <v>2.22610759735107</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.36545991897583</v>
       </c>
       <c r="G337" t="n">
-        <v>2.41453099250793</v>
+        <v>2.41453075408936</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.29235696792603</v>
       </c>
       <c r="G339" t="n">
-        <v>2.36208343505859</v>
+        <v>2.36208319664001</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.39456605911255</v>
       </c>
       <c r="G341" t="n">
-        <v>2.43541288375854</v>
+        <v>2.43541264533997</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.36004495620728</v>
       </c>
       <c r="G342" t="n">
-        <v>2.41064596176147</v>
+        <v>2.4106457233429</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.53332710266113</v>
       </c>
       <c r="G344" t="n">
-        <v>2.53496623039246</v>
+        <v>2.53496599197388</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.44533205032349</v>
       </c>
       <c r="G345" t="n">
-        <v>2.47183465957642</v>
+        <v>2.47183442115784</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.22466802597046</v>
       </c>
       <c r="G347" t="n">
-        <v>2.31352043151855</v>
+        <v>2.31352066993713</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.17322492599487</v>
       </c>
       <c r="G348" t="n">
-        <v>2.27661228179932</v>
+        <v>2.27661275863647</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.20165395736694</v>
       </c>
       <c r="G349" t="n">
-        <v>2.29700922966003</v>
+        <v>2.29700899124146</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.28964900970459</v>
       </c>
       <c r="G350" t="n">
-        <v>2.36014103889465</v>
+        <v>2.3601405620575</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.1244900226593</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24164819717407</v>
+        <v>2.24164843559265</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.17187190055847</v>
       </c>
       <c r="G354" t="n">
-        <v>2.27564167976379</v>
+        <v>2.27564215660095</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.11636710166931</v>
       </c>
       <c r="G355" t="n">
-        <v>2.26481938362122</v>
+        <v>2.26481986045837</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.11772108078003</v>
       </c>
       <c r="G356" t="n">
-        <v>2.26580333709717</v>
+        <v>2.26580309867859</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.02566504478455</v>
       </c>
       <c r="G360" t="n">
-        <v>2.19890189170837</v>
+        <v>2.19890165328979</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.02701902389526</v>
       </c>
       <c r="G361" t="n">
-        <v>2.19988560676575</v>
+        <v>2.19988536834717</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.95120811462402</v>
       </c>
       <c r="G362" t="n">
-        <v>2.14478993415833</v>
+        <v>2.1447901725769</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.01348090171814</v>
       </c>
       <c r="G363" t="n">
-        <v>2.19004678726196</v>
+        <v>2.19004654884338</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.92142510414124</v>
       </c>
       <c r="G365" t="n">
-        <v>2.12314510345459</v>
+        <v>2.12314534187317</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.87675094604492</v>
       </c>
       <c r="G366" t="n">
-        <v>2.09067869186401</v>
+        <v>2.09067845344543</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.98911309242249</v>
       </c>
       <c r="G368" t="n">
-        <v>2.17233753204346</v>
+        <v>2.17233729362488</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.91736388206482</v>
       </c>
       <c r="G370" t="n">
-        <v>2.12019395828247</v>
+        <v>2.12019371986389</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.9904670715332</v>
       </c>
       <c r="G371" t="n">
-        <v>2.17332172393799</v>
+        <v>2.17332196235657</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.96068406105042</v>
       </c>
       <c r="G372" t="n">
-        <v>2.15167689323425</v>
+        <v>2.15167665481567</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.92142510414124</v>
       </c>
       <c r="G373" t="n">
-        <v>2.12314510345459</v>
+        <v>2.12314534187317</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.82666110992432</v>
       </c>
       <c r="G374" t="n">
-        <v>2.05427551269531</v>
+        <v>2.05427527427673</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.77115702629089</v>
       </c>
       <c r="G376" t="n">
-        <v>2.01393795013428</v>
+        <v>2.01393818855286</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.89570307731628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.10445213317871</v>
+        <v>2.10445165634155</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.87675094604492</v>
       </c>
       <c r="G378" t="n">
-        <v>2.09067869186401</v>
+        <v>2.09067845344543</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.9593300819397</v>
       </c>
       <c r="G380" t="n">
-        <v>2.1506929397583</v>
+        <v>2.15069270133972</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.95526909828186</v>
       </c>
       <c r="G384" t="n">
-        <v>2.14774107933044</v>
+        <v>2.1477415561676</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.25309705734253</v>
       </c>
       <c r="G386" t="n">
-        <v>2.3641881942749</v>
+        <v>2.36418771743774</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.17457890510559</v>
       </c>
       <c r="G387" t="n">
-        <v>2.30712485313416</v>
+        <v>2.30712509155273</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.18270206451416</v>
       </c>
       <c r="G388" t="n">
-        <v>2.31302833557129</v>
+        <v>2.31302857398987</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.27475810050964</v>
       </c>
       <c r="G391" t="n">
-        <v>2.37993025779724</v>
+        <v>2.37992978096008</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.34380006790161</v>
       </c>
       <c r="G392" t="n">
-        <v>2.4301061630249</v>
+        <v>2.43010592460632</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.28288006782532</v>
       </c>
       <c r="G397" t="n">
-        <v>2.38583254814148</v>
+        <v>2.38583278656006</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.28288006782532</v>
       </c>
       <c r="G398" t="n">
-        <v>2.38583254814148</v>
+        <v>2.38583278656006</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.12178206443787</v>
       </c>
       <c r="G402" t="n">
-        <v>2.26875448226929</v>
+        <v>2.26875472068787</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.16780996322632</v>
       </c>
       <c r="G403" t="n">
-        <v>2.30220508575439</v>
+        <v>2.30220556259155</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.18405508995056</v>
       </c>
       <c r="G404" t="n">
-        <v>2.3140115737915</v>
+        <v>2.31401181221008</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.14885711669922</v>
       </c>
       <c r="G405" t="n">
-        <v>2.28843140602112</v>
+        <v>2.2884316444397</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.16780996322632</v>
       </c>
       <c r="G406" t="n">
-        <v>2.30220508575439</v>
+        <v>2.30220556259155</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G407" t="n">
-        <v>2.28449606895447</v>
+        <v>2.28449583053589</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.39794993400574</v>
       </c>
       <c r="G409" t="n">
-        <v>2.46945977210999</v>
+        <v>2.46945953369141</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.35192203521729</v>
       </c>
       <c r="G410" t="n">
-        <v>2.4360089302063</v>
+        <v>2.43600869178772</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.32755494117737</v>
       </c>
       <c r="G412" t="n">
-        <v>2.41830015182495</v>
+        <v>2.41829991340637</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.25309705734253</v>
       </c>
       <c r="G413" t="n">
-        <v>2.3641881942749</v>
+        <v>2.36418771743774</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.25309705734253</v>
       </c>
       <c r="G415" t="n">
-        <v>2.3641881942749</v>
+        <v>2.36418771743774</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.30183291435242</v>
       </c>
       <c r="G417" t="n">
-        <v>2.39960670471191</v>
+        <v>2.39960646629333</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.32755494117737</v>
       </c>
       <c r="G418" t="n">
-        <v>2.41830015182495</v>
+        <v>2.41829991340637</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.26528096199036</v>
       </c>
       <c r="G419" t="n">
-        <v>2.37304282188416</v>
+        <v>2.373042345047</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.22196102142334</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34155964851379</v>
+        <v>2.34155941009521</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.18134808540344</v>
       </c>
       <c r="G421" t="n">
-        <v>2.31204414367676</v>
+        <v>2.31204438209534</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.21248388290405</v>
       </c>
       <c r="G422" t="n">
-        <v>2.33467245101929</v>
+        <v>2.33467221260071</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.22602200508118</v>
       </c>
       <c r="G424" t="n">
-        <v>2.34451103210449</v>
+        <v>2.34451079368591</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.17593288421631</v>
       </c>
       <c r="G426" t="n">
-        <v>2.30810904502869</v>
+        <v>2.30810832977295</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.20300793647766</v>
       </c>
       <c r="G427" t="n">
-        <v>2.32778573036194</v>
+        <v>2.32778596878052</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.24632906913757</v>
       </c>
       <c r="G428" t="n">
-        <v>2.35926938056946</v>
+        <v>2.35926914215088</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.19759297370911</v>
       </c>
       <c r="G429" t="n">
-        <v>2.32385015487671</v>
+        <v>2.32384991645813</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.14750409126282</v>
       </c>
       <c r="G430" t="n">
-        <v>2.2874481678009</v>
+        <v>2.28744840621948</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.11772108078003</v>
       </c>
       <c r="G431" t="n">
-        <v>2.26580333709717</v>
+        <v>2.26580309867859</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.15427303314209</v>
       </c>
       <c r="G434" t="n">
-        <v>2.29236745834351</v>
+        <v>2.29236769676208</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.25174403190613</v>
       </c>
       <c r="G435" t="n">
-        <v>2.36320447921753</v>
+        <v>2.36320495605469</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.25309705734253</v>
       </c>
       <c r="G436" t="n">
-        <v>2.3641881942749</v>
+        <v>2.36418771743774</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.186763048172</v>
       </c>
       <c r="G437" t="n">
-        <v>2.31597948074341</v>
+        <v>2.31597971916199</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.10553693771362</v>
       </c>
       <c r="G438" t="n">
-        <v>2.25694823265076</v>
+        <v>2.25694847106934</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.17457890510559</v>
       </c>
       <c r="G441" t="n">
-        <v>2.30712485313416</v>
+        <v>2.30712509155273</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.17187190055847</v>
       </c>
       <c r="G442" t="n">
-        <v>2.30515694618225</v>
+        <v>2.30515742301941</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.1664559841156</v>
       </c>
       <c r="G444" t="n">
-        <v>2.30122184753418</v>
+        <v>2.3012216091156</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.2598659992218</v>
       </c>
       <c r="G445" t="n">
-        <v>2.36910700798035</v>
+        <v>2.36910653114319</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.4825611114502</v>
       </c>
       <c r="G449" t="n">
-        <v>2.53095102310181</v>
+        <v>2.53095078468323</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.47240710258484</v>
       </c>
       <c r="G450" t="n">
-        <v>2.52357149124146</v>
+        <v>2.52357125282288</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.36952090263367</v>
       </c>
       <c r="G451" t="n">
-        <v>2.44879865646362</v>
+        <v>2.4487988948822</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.31266307830811</v>
       </c>
       <c r="G452" t="n">
-        <v>2.40747761726379</v>
+        <v>2.40747737884521</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.02701902389526</v>
       </c>
       <c r="G455" t="n">
-        <v>2.19988560676575</v>
+        <v>2.19988536834717</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.00671195983887</v>
       </c>
       <c r="G459" t="n">
-        <v>2.18512749671936</v>
+        <v>2.18512773513794</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.96474504470825</v>
       </c>
       <c r="G461" t="n">
-        <v>2.15462803840637</v>
+        <v>2.15462779998779</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.86998200416565</v>
       </c>
       <c r="G462" t="n">
-        <v>2.08575892448425</v>
+        <v>2.08575940132141</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.87945795059204</v>
       </c>
       <c r="G463" t="n">
-        <v>2.09264540672302</v>
+        <v>2.0926456451416</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.92142510414124</v>
       </c>
       <c r="G464" t="n">
-        <v>2.12314510345459</v>
+        <v>2.12314534187317</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G465" t="n">
-        <v>2.11330628395081</v>
+        <v>2.11330676078796</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.87675094604492</v>
       </c>
       <c r="G466" t="n">
-        <v>2.09067869186401</v>
+        <v>2.09067845344543</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.8753969669342</v>
       </c>
       <c r="G467" t="n">
-        <v>2.08969449996948</v>
+        <v>2.08969402313232</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.83072304725647</v>
       </c>
       <c r="G468" t="n">
-        <v>2.05722737312317</v>
+        <v>2.05722784996033</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.84561395645142</v>
       </c>
       <c r="G469" t="n">
-        <v>2.06804943084717</v>
+        <v>2.06804990768433</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.83207607269287</v>
       </c>
       <c r="G470" t="n">
-        <v>2.05821084976196</v>
+        <v>2.05821108818054</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.92684006690979</v>
       </c>
       <c r="G472" t="n">
-        <v>2.1270809173584</v>
+        <v>2.12708044052124</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.80635499954224</v>
       </c>
       <c r="G474" t="n">
-        <v>2.03951811790466</v>
+        <v>2.03951835632324</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.75355792045593</v>
       </c>
       <c r="G475" t="n">
-        <v>2.00114798545837</v>
+        <v>2.00114774703979</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.63307309150696</v>
       </c>
       <c r="G476" t="n">
-        <v>1.91358554363251</v>
+        <v>1.91358530521393</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.89435005187988</v>
       </c>
       <c r="G477" t="n">
-        <v>2.10346865653992</v>
+        <v>2.10346841812134</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.86321306228638</v>
       </c>
       <c r="G478" t="n">
-        <v>2.08083987236023</v>
+        <v>2.08083963394165</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.88893508911133</v>
       </c>
       <c r="G479" t="n">
-        <v>2.09953308105469</v>
+        <v>2.09953331947327</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.8848729133606</v>
       </c>
       <c r="G481" t="n">
-        <v>2.09658098220825</v>
+        <v>2.09658074378967</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.80635499954224</v>
       </c>
       <c r="G482" t="n">
-        <v>2.03951811790466</v>
+        <v>2.03951835632324</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.78875589370728</v>
       </c>
       <c r="G483" t="n">
-        <v>2.02672791481018</v>
+        <v>2.0267276763916</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.79552507400513</v>
       </c>
       <c r="G485" t="n">
-        <v>2.03164744377136</v>
+        <v>2.03164768218994</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.79552507400513</v>
       </c>
       <c r="G487" t="n">
-        <v>2.03164744377136</v>
+        <v>2.03164768218994</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.9593300819397</v>
       </c>
       <c r="G488" t="n">
-        <v>2.1506929397583</v>
+        <v>2.15069270133972</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.86185908317566</v>
       </c>
       <c r="G489" t="n">
-        <v>2.07985591888428</v>
+        <v>2.0798556804657</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.86998200416565</v>
       </c>
       <c r="G490" t="n">
-        <v>2.08575892448425</v>
+        <v>2.08575940132141</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.99452805519104</v>
       </c>
       <c r="G491" t="n">
-        <v>2.17627286911011</v>
+        <v>2.17627310752869</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.11095190048218</v>
       </c>
       <c r="G492" t="n">
-        <v>2.26088404655457</v>
+        <v>2.26088380813599</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.01889610290527</v>
       </c>
       <c r="G493" t="n">
-        <v>2.19398236274719</v>
+        <v>2.19398260116577</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.186763048172</v>
       </c>
       <c r="G498" t="n">
-        <v>2.31597948074341</v>
+        <v>2.31597971916199</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.18270206451416</v>
       </c>
       <c r="G499" t="n">
-        <v>2.31302833557129</v>
+        <v>2.31302857398987</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.071692943573</v>
       </c>
       <c r="G500" t="n">
-        <v>2.23235249519348</v>
+        <v>2.2323522567749</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.87810397148132</v>
       </c>
       <c r="G501" t="n">
-        <v>2.09166193008423</v>
+        <v>2.09166169166565</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.80635499954224</v>
       </c>
       <c r="G503" t="n">
-        <v>2.03951811790466</v>
+        <v>2.03951835632324</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.81312394142151</v>
       </c>
       <c r="G504" t="n">
-        <v>2.04443764686584</v>
+        <v>2.04443740844727</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.90653395652771</v>
       </c>
       <c r="G505" t="n">
-        <v>2.11232304573059</v>
+        <v>2.11232328414917</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.89299607276917</v>
       </c>
       <c r="G507" t="n">
-        <v>2.10248422622681</v>
+        <v>2.10248446464539</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.83613801002502</v>
       </c>
       <c r="G508" t="n">
-        <v>2.06116318702698</v>
+        <v>2.0611629486084</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.85102891921997</v>
       </c>
       <c r="G509" t="n">
-        <v>2.07198476791382</v>
+        <v>2.0719850063324</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.84967494010925</v>
       </c>
       <c r="G511" t="n">
-        <v>2.07100105285645</v>
+        <v>2.07100081443787</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.81583094596863</v>
       </c>
       <c r="G512" t="n">
-        <v>2.04640483856201</v>
+        <v>2.04640507698059</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.79552507400513</v>
       </c>
       <c r="G513" t="n">
-        <v>2.03164744377136</v>
+        <v>2.03164768218994</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.87133598327637</v>
       </c>
       <c r="G514" t="n">
-        <v>2.08674287796021</v>
+        <v>2.08674311637878</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.87810397148132</v>
       </c>
       <c r="G515" t="n">
-        <v>2.09166193008423</v>
+        <v>2.09166169166565</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.08658409118652</v>
       </c>
       <c r="G520" t="n">
-        <v>2.24317455291748</v>
+        <v>2.24317479133606</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.10553693771362</v>
       </c>
       <c r="G521" t="n">
-        <v>2.25694823265076</v>
+        <v>2.25694847106934</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.99317407608032</v>
       </c>
       <c r="G523" t="n">
-        <v>2.17528891563416</v>
+        <v>2.17528867721558</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.01889610290527</v>
       </c>
       <c r="G525" t="n">
-        <v>2.19398236274719</v>
+        <v>2.19398260116577</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.13125896453857</v>
       </c>
       <c r="G527" t="n">
-        <v>2.27564167976379</v>
+        <v>2.27564215660095</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.17931699752808</v>
       </c>
       <c r="G533" t="n">
-        <v>2.31056809425354</v>
+        <v>2.31056833267212</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.06898498535156</v>
       </c>
       <c r="G536" t="n">
-        <v>2.230384349823</v>
+        <v>2.23038411140442</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.18811702728271</v>
       </c>
       <c r="G538" t="n">
-        <v>2.31696391105652</v>
+        <v>2.31696343421936</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.17593288421631</v>
       </c>
       <c r="G540" t="n">
-        <v>2.30810904502869</v>
+        <v>2.30810832977295</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.11907505989075</v>
       </c>
       <c r="G541" t="n">
-        <v>2.2667875289917</v>
+        <v>2.26678729057312</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.0777850151062</v>
       </c>
       <c r="G542" t="n">
-        <v>2.23677968978882</v>
+        <v>2.23678016662598</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.24362111091614</v>
       </c>
       <c r="G544" t="n">
-        <v>2.35730123519897</v>
+        <v>2.3573009967804</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.25174403190613</v>
       </c>
       <c r="G545" t="n">
-        <v>2.36320447921753</v>
+        <v>2.36320495605469</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.22602200508118</v>
       </c>
       <c r="G547" t="n">
-        <v>2.34451103210449</v>
+        <v>2.34451079368591</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.23549795150757</v>
       </c>
       <c r="G548" t="n">
-        <v>2.35139775276184</v>
+        <v>2.35139751434326</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.29168009757996</v>
       </c>
       <c r="G550" t="n">
-        <v>2.39222836494446</v>
+        <v>2.39222812652588</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.29844903945923</v>
       </c>
       <c r="G552" t="n">
-        <v>2.39714741706848</v>
+        <v>2.3971471786499</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.05477094650269</v>
       </c>
       <c r="G556" t="n">
-        <v>2.22005414962769</v>
+        <v>2.22005438804626</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.17999410629272</v>
       </c>
       <c r="G558" t="n">
-        <v>2.31106019020081</v>
+        <v>2.31106042861938</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.22331500053406</v>
       </c>
       <c r="G559" t="n">
-        <v>2.34254360198975</v>
+        <v>2.34254384040833</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.14750409126282</v>
       </c>
       <c r="G565" t="n">
-        <v>2.2874481678009</v>
+        <v>2.28744840621948</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G567" t="n">
-        <v>2.2982702255249</v>
+        <v>2.29826998710632</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.14073491096497</v>
       </c>
       <c r="G568" t="n">
-        <v>2.28252863883972</v>
+        <v>2.2825288772583</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.08861494064331</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24465012550354</v>
+        <v>2.2446506023407</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.05680108070374</v>
       </c>
       <c r="G575" t="n">
-        <v>2.22152996063232</v>
+        <v>2.22152972221375</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.17999410629272</v>
       </c>
       <c r="G579" t="n">
-        <v>2.31106019020081</v>
+        <v>2.31106042861938</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.18947005271912</v>
       </c>
       <c r="G580" t="n">
-        <v>2.31794714927673</v>
+        <v>2.31794691085815</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.14750409126282</v>
       </c>
       <c r="G581" t="n">
-        <v>2.2874481678009</v>
+        <v>2.28744840621948</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.186763048172</v>
       </c>
       <c r="G582" t="n">
-        <v>2.31597948074341</v>
+        <v>2.31597971916199</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.20165395736694</v>
       </c>
       <c r="G583" t="n">
-        <v>2.32680177688599</v>
+        <v>2.32680153846741</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.23414492607117</v>
       </c>
       <c r="G584" t="n">
-        <v>2.35041403770447</v>
+        <v>2.35041427612305</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.30318689346313</v>
       </c>
       <c r="G585" t="n">
-        <v>2.40059089660645</v>
+        <v>2.40059065818787</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.30792498588562</v>
       </c>
       <c r="G588" t="n">
-        <v>2.40403437614441</v>
+        <v>2.40403389930725</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.30792498588562</v>
       </c>
       <c r="G589" t="n">
-        <v>2.40403437614441</v>
+        <v>2.40403389930725</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.24768209457397</v>
       </c>
       <c r="G590" t="n">
-        <v>2.36025238037109</v>
+        <v>2.36025261878967</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.2070689201355</v>
       </c>
       <c r="G591" t="n">
-        <v>2.33073687553406</v>
+        <v>2.33073663711548</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.2118079662323</v>
       </c>
       <c r="G593" t="n">
-        <v>2.33418107032776</v>
+        <v>2.33418083190918</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.24362111091614</v>
       </c>
       <c r="G594" t="n">
-        <v>2.35730123519897</v>
+        <v>2.3573009967804</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.22805309295654</v>
       </c>
       <c r="G595" t="n">
-        <v>2.34598684310913</v>
+        <v>2.34598731994629</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.17457890510559</v>
       </c>
       <c r="G596" t="n">
-        <v>2.30712485313416</v>
+        <v>2.30712509155273</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.19353199005127</v>
       </c>
       <c r="G598" t="n">
-        <v>2.32089877128601</v>
+        <v>2.32089900970459</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.33161592483521</v>
       </c>
       <c r="G601" t="n">
-        <v>2.42125129699707</v>
+        <v>2.42125153541565</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.39659690856934</v>
       </c>
       <c r="G602" t="n">
-        <v>2.46847653388977</v>
+        <v>2.46847629547119</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.44533205032349</v>
       </c>
       <c r="G603" t="n">
-        <v>2.50389456748962</v>
+        <v>2.5038948059082</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G609" t="n">
-        <v>2.35375952720642</v>
+        <v>2.35375928878784</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.15765690803528</v>
       </c>
       <c r="G611" t="n">
-        <v>2.35023283958435</v>
+        <v>2.35023307800293</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.09402990341187</v>
       </c>
       <c r="G612" t="n">
-        <v>2.30287551879883</v>
+        <v>2.30287528038025</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.91330194473267</v>
       </c>
       <c r="G613" t="n">
-        <v>2.16836023330688</v>
+        <v>2.16836047172546</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.77657198905945</v>
       </c>
       <c r="G615" t="n">
-        <v>2.06659293174744</v>
+        <v>2.06659269332886</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.7772490978241</v>
       </c>
       <c r="G616" t="n">
-        <v>2.06709694862366</v>
+        <v>2.06709671020508</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G618" t="n">
-        <v>2.16433000564575</v>
+        <v>2.16433024406433</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G619" t="n">
-        <v>2.09077525138855</v>
+        <v>2.09077477455139</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.86185908317566</v>
       </c>
       <c r="G621" t="n">
-        <v>2.13007164001465</v>
+        <v>2.13007140159607</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.98775911331177</v>
       </c>
       <c r="G625" t="n">
-        <v>2.22377848625183</v>
+        <v>2.22377872467041</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.02431106567383</v>
       </c>
       <c r="G626" t="n">
-        <v>2.25098443031311</v>
+        <v>2.25098419189453</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.93090105056763</v>
       </c>
       <c r="G628" t="n">
-        <v>2.1814591884613</v>
+        <v>2.18145895004272</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.01551198959351</v>
       </c>
       <c r="G631" t="n">
-        <v>2.24443483352661</v>
+        <v>2.24443507194519</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.1711950302124</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36030912399292</v>
+        <v>2.3603093624115</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G635" t="n">
-        <v>2.33965301513672</v>
+        <v>2.33965277671814</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.17187190055847</v>
       </c>
       <c r="G636" t="n">
-        <v>2.36081266403198</v>
+        <v>2.36081314086914</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G638" t="n">
-        <v>2.33965301513672</v>
+        <v>2.33965277671814</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G641" t="n">
-        <v>2.35577487945557</v>
+        <v>2.35577535629272</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.22737598419189</v>
       </c>
       <c r="G642" t="n">
-        <v>2.40212464332581</v>
+        <v>2.40212488174438</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.238205909729</v>
       </c>
       <c r="G643" t="n">
-        <v>2.41018533706665</v>
+        <v>2.41018557548523</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.12245893478394</v>
       </c>
       <c r="G645" t="n">
-        <v>2.32403516769409</v>
+        <v>2.32403540611267</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G646" t="n">
-        <v>2.35375952720642</v>
+        <v>2.35375928878784</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G648" t="n">
-        <v>2.35577487945557</v>
+        <v>2.35577535629272</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.18743991851807</v>
       </c>
       <c r="G649" t="n">
-        <v>2.37240052223206</v>
+        <v>2.37240028381348</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G650" t="n">
-        <v>2.35375952720642</v>
+        <v>2.35375928878784</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.09402990341187</v>
       </c>
       <c r="G652" t="n">
-        <v>2.30287551879883</v>
+        <v>2.30287528038025</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.13193488121033</v>
       </c>
       <c r="G655" t="n">
-        <v>2.33108806610107</v>
+        <v>2.33108830451965</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.17796301841736</v>
       </c>
       <c r="G656" t="n">
-        <v>2.36534667015076</v>
+        <v>2.36534643173218</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.23617506027222</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40867376327515</v>
+        <v>2.40867352485657</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.22128391265869</v>
       </c>
       <c r="G660" t="n">
-        <v>2.39759039878845</v>
+        <v>2.39759016036987</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.0980908870697</v>
       </c>
       <c r="G662" t="n">
-        <v>2.3058979511261</v>
+        <v>2.30589842796326</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.12719702720642</v>
       </c>
       <c r="G664" t="n">
-        <v>2.32756161689758</v>
+        <v>2.32756185531616</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.90924096107483</v>
       </c>
       <c r="G666" t="n">
-        <v>2.16533780097961</v>
+        <v>2.16533756256104</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.7975549697876</v>
       </c>
       <c r="G668" t="n">
-        <v>2.08221054077148</v>
+        <v>2.08221030235291</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.77115702629089</v>
       </c>
       <c r="G669" t="n">
-        <v>2.06256246566772</v>
+        <v>2.0625627040863</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.70753002166748</v>
       </c>
       <c r="G671" t="n">
-        <v>2.0152051448822</v>
+        <v>2.01520490646362</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.70820689201355</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01570844650269</v>
+        <v>2.01570892333984</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.74543499946594</v>
       </c>
       <c r="G675" t="n">
-        <v>2.04341793060303</v>
+        <v>2.04341769218445</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.6838390827179</v>
       </c>
       <c r="G678" t="n">
-        <v>1.99757206439972</v>
+        <v>1.99757182598114</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.70076107978821</v>
       </c>
       <c r="G679" t="n">
-        <v>2.01016712188721</v>
+        <v>2.01016688346863</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.58366107940674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.92300999164581</v>
+        <v>1.92300975322723</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.67842388153076</v>
       </c>
       <c r="G683" t="n">
-        <v>1.9935417175293</v>
+        <v>1.99354147911072</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.79281711578369</v>
       </c>
       <c r="G684" t="n">
-        <v>2.07868385314941</v>
+        <v>2.07868409156799</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.77657198905945</v>
       </c>
       <c r="G686" t="n">
-        <v>2.06659293174744</v>
+        <v>2.06659269332886</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.87268900871277</v>
       </c>
       <c r="G687" t="n">
-        <v>2.13813257217407</v>
+        <v>2.13813233375549</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.86118197441101</v>
       </c>
       <c r="G689" t="n">
-        <v>2.12956786155701</v>
+        <v>2.12956738471985</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.85170602798462</v>
       </c>
       <c r="G690" t="n">
-        <v>2.12251496315002</v>
+        <v>2.12251472473145</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.87268900871277</v>
       </c>
       <c r="G691" t="n">
-        <v>2.13813257217407</v>
+        <v>2.13813233375549</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G692" t="n">
-        <v>2.16433000564575</v>
+        <v>2.16433024406433</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.91736388206482</v>
       </c>
       <c r="G693" t="n">
-        <v>2.17138385772705</v>
+        <v>2.17138361930847</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.96136093139648</v>
       </c>
       <c r="G694" t="n">
-        <v>2.20413064956665</v>
+        <v>2.20413041114807</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.93360900878906</v>
       </c>
       <c r="G695" t="n">
-        <v>2.18347477912903</v>
+        <v>2.18347454071045</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.69940710067749</v>
       </c>
       <c r="G701" t="n">
-        <v>2.00915932655334</v>
+        <v>2.00915956497192</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.51461791992188</v>
       </c>
       <c r="G704" t="n">
-        <v>1.87162125110626</v>
+        <v>1.87162148952484</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.48415899276733</v>
       </c>
       <c r="G706" t="n">
-        <v>1.84895086288452</v>
+        <v>1.84895074367523</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.44286894798279</v>
       </c>
       <c r="G707" t="n">
-        <v>1.81821858882904</v>
+        <v>1.81821882724762</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.3941330909729</v>
       </c>
       <c r="G708" t="n">
-        <v>1.78194510936737</v>
+        <v>1.78194499015808</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.44625306129456</v>
       </c>
       <c r="G709" t="n">
-        <v>1.82073748111725</v>
+        <v>1.82073771953583</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G710" t="n">
-        <v>1.78647887706757</v>
+        <v>1.78647875785828</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.43542289733887</v>
       </c>
       <c r="G712" t="n">
-        <v>1.81267642974854</v>
+        <v>1.81267666816711</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.41443991661072</v>
       </c>
       <c r="G713" t="n">
-        <v>1.79705893993378</v>
+        <v>1.79705917835236</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G715" t="n">
-        <v>1.76078522205353</v>
+        <v>1.76078546047211</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.37450408935547</v>
       </c>
       <c r="G716" t="n">
-        <v>1.76733529567719</v>
+        <v>1.76733505725861</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.28786301612854</v>
       </c>
       <c r="G717" t="n">
-        <v>1.70284855365753</v>
+        <v>1.70284843444824</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.17482304573059</v>
       </c>
       <c r="G719" t="n">
-        <v>1.61871302127838</v>
+        <v>1.61871325969696</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.20799088478088</v>
       </c>
       <c r="G721" t="n">
-        <v>1.64339971542358</v>
+        <v>1.64339995384216</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.29192399978638</v>
       </c>
       <c r="G723" t="n">
-        <v>1.70587110519409</v>
+        <v>1.7058709859848</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.28650903701782</v>
       </c>
       <c r="G725" t="n">
-        <v>1.70184075832367</v>
+        <v>1.70184063911438</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.37924194335938</v>
       </c>
       <c r="G726" t="n">
-        <v>1.77086138725281</v>
+        <v>1.7708615064621</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.29733896255493</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70990145206451</v>
+        <v>1.70990133285522</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.28041696548462</v>
       </c>
       <c r="G728" t="n">
-        <v>1.69730627536774</v>
+        <v>1.69730639457703</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.32170701026917</v>
       </c>
       <c r="G729" t="n">
-        <v>1.72803831100464</v>
+        <v>1.72803843021393</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G730" t="n">
-        <v>1.74113702774048</v>
+        <v>1.74113750457764</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.36028909683228</v>
       </c>
       <c r="G731" t="n">
-        <v>1.75675487518311</v>
+        <v>1.75675511360168</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G733" t="n">
-        <v>1.76078522205353</v>
+        <v>1.76078546047211</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.29260110855103</v>
       </c>
       <c r="G737" t="n">
-        <v>1.70637476444244</v>
+        <v>1.70637500286102</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.26620292663574</v>
       </c>
       <c r="G738" t="n">
-        <v>1.68672680854797</v>
+        <v>1.68672657012939</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.34810495376587</v>
       </c>
       <c r="G739" t="n">
-        <v>1.74768626689911</v>
+        <v>1.7476863861084</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.36299705505371</v>
       </c>
       <c r="G741" t="n">
-        <v>1.75877058506012</v>
+        <v>1.75877046585083</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.48957395553589</v>
       </c>
       <c r="G742" t="n">
-        <v>1.85298097133636</v>
+        <v>1.85298120975494</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.40225601196289</v>
       </c>
       <c r="G743" t="n">
-        <v>1.78799068927765</v>
+        <v>1.78799057006836</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.42391610145569</v>
       </c>
       <c r="G744" t="n">
-        <v>1.80411207675934</v>
+        <v>1.80411219596863</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G745" t="n">
-        <v>1.78647887706757</v>
+        <v>1.78647875785828</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.43610000610352</v>
       </c>
       <c r="G746" t="n">
-        <v>1.81318080425262</v>
+        <v>1.81318056583405</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.5484631061554</v>
       </c>
       <c r="G747" t="n">
-        <v>1.89681231975555</v>
+        <v>1.89681208133698</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.50514197349548</v>
       </c>
       <c r="G748" t="n">
-        <v>1.86456823348999</v>
+        <v>1.86456859111786</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.47062110900879</v>
       </c>
       <c r="G750" t="n">
-        <v>1.83887457847595</v>
+        <v>1.83887481689453</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.39007210731506</v>
       </c>
       <c r="G752" t="n">
-        <v>1.77892220020294</v>
+        <v>1.77892231941223</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G753" t="n">
-        <v>1.74113702774048</v>
+        <v>1.74113750457764</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.36705803871155</v>
       </c>
       <c r="G754" t="n">
-        <v>1.76179301738739</v>
+        <v>1.7617928981781</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.35758209228516</v>
       </c>
       <c r="G755" t="n">
-        <v>1.75473999977112</v>
+        <v>1.75473988056183</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.27567911148071</v>
       </c>
       <c r="G757" t="n">
-        <v>1.69377994537354</v>
+        <v>1.69377970695496</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.26484894752502</v>
       </c>
       <c r="G758" t="n">
-        <v>1.68571925163269</v>
+        <v>1.6857191324234</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.31087708473206</v>
       </c>
       <c r="G759" t="n">
-        <v>1.71997785568237</v>
+        <v>1.71997773647308</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.24995708465576</v>
       </c>
       <c r="G761" t="n">
-        <v>1.67463505268097</v>
+        <v>1.67463493347168</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.21949791908264</v>
       </c>
       <c r="G762" t="n">
-        <v>1.65196442604065</v>
+        <v>1.65196454524994</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.27703309059143</v>
       </c>
       <c r="G763" t="n">
-        <v>1.69478762149811</v>
+        <v>1.6947877407074</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.21611309051514</v>
       </c>
       <c r="G765" t="n">
-        <v>1.64944529533386</v>
+        <v>1.64944517612457</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.29057002067566</v>
       </c>
       <c r="G766" t="n">
-        <v>1.70486307144165</v>
+        <v>1.70486330986023</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.25401902198792</v>
       </c>
       <c r="G768" t="n">
-        <v>1.67765855789185</v>
+        <v>1.67765843868256</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.25131106376648</v>
       </c>
       <c r="G770" t="n">
-        <v>1.67564296722412</v>
+        <v>1.67564284801483</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.21340608596802</v>
       </c>
       <c r="G771" t="n">
-        <v>1.6474301815033</v>
+        <v>1.64743041992188</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.071937084198</v>
       </c>
       <c r="G774" t="n">
-        <v>1.54213547706604</v>
+        <v>1.54213571548462</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.08006000518799</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54818153381348</v>
+        <v>1.54818141460419</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.06719899177551</v>
       </c>
       <c r="G778" t="n">
-        <v>1.53860878944397</v>
+        <v>1.53860902786255</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.11187291145325</v>
       </c>
       <c r="G783" t="n">
-        <v>1.57185971736908</v>
+        <v>1.5718594789505</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.13014888763428</v>
       </c>
       <c r="G784" t="n">
-        <v>1.58546221256256</v>
+        <v>1.58546233177185</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.00086498260498</v>
       </c>
       <c r="G785" t="n">
-        <v>1.48923671245575</v>
+        <v>1.48923683166504</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.06110692024231</v>
       </c>
       <c r="G789" t="n">
-        <v>1.53407466411591</v>
+        <v>1.53407454490662</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.37585806846619</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76834261417389</v>
+        <v>1.76834285259247</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.37450408935547</v>
       </c>
       <c r="G798" t="n">
-        <v>1.76733529567719</v>
+        <v>1.76733505725861</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.35555100440979</v>
       </c>
       <c r="G799" t="n">
-        <v>1.75322842597961</v>
+        <v>1.75322830677032</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.31764602661133</v>
       </c>
       <c r="G800" t="n">
-        <v>1.72501575946808</v>
+        <v>1.72501587867737</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.34472107887268</v>
       </c>
       <c r="G801" t="n">
-        <v>1.74516749382019</v>
+        <v>1.74516761302948</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G802" t="n">
-        <v>1.76280069351196</v>
+        <v>1.76280045509338</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.38398003578186</v>
       </c>
       <c r="G803" t="n">
-        <v>1.77438819408417</v>
+        <v>1.77438807487488</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.44828391075134</v>
       </c>
       <c r="G804" t="n">
-        <v>1.82224893569946</v>
+        <v>1.82224917411804</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.51461791992188</v>
       </c>
       <c r="G805" t="n">
-        <v>1.87162125110626</v>
+        <v>1.87162148952484</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.50311088562012</v>
       </c>
       <c r="G806" t="n">
-        <v>1.86305665969849</v>
+        <v>1.86305642127991</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.37924194335938</v>
       </c>
       <c r="G811" t="n">
-        <v>1.77086138725281</v>
+        <v>1.7708615064621</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G813" t="n">
-        <v>1.78244888782501</v>
+        <v>1.78244864940643</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.40902495384216</v>
       </c>
       <c r="G814" t="n">
-        <v>1.79302859306335</v>
+        <v>1.79302871227264</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.44286894798279</v>
       </c>
       <c r="G816" t="n">
-        <v>1.81821858882904</v>
+        <v>1.81821882724762</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.52680206298828</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88069033622742</v>
+        <v>1.88068985939026</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.50446510314941</v>
       </c>
       <c r="G820" t="n">
-        <v>1.86406457424164</v>
+        <v>1.86406481266022</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.46994400024414</v>
       </c>
       <c r="G821" t="n">
-        <v>1.83837068080902</v>
+        <v>1.83837056159973</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.4597909450531</v>
       </c>
       <c r="G822" t="n">
-        <v>1.83081376552582</v>
+        <v>1.83081352710724</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.43880796432495</v>
       </c>
       <c r="G823" t="n">
-        <v>1.81519639492035</v>
+        <v>1.81519627571106</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.47739005088806</v>
       </c>
       <c r="G824" t="n">
-        <v>1.84391260147095</v>
+        <v>1.84391283988953</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.49837303161621</v>
       </c>
       <c r="G827" t="n">
-        <v>1.85953044891357</v>
+        <v>1.859530210495</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.49837303161621</v>
       </c>
       <c r="G829" t="n">
-        <v>1.85953044891357</v>
+        <v>1.859530210495</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.50378799438477</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86356067657471</v>
+        <v>1.86356043815613</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.56944608688354</v>
       </c>
       <c r="G835" t="n">
-        <v>1.91243016719818</v>
+        <v>1.91242969036102</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.83139991760254</v>
       </c>
       <c r="G840" t="n">
-        <v>2.10740089416504</v>
+        <v>2.1074013710022</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.82463097572327</v>
       </c>
       <c r="G843" t="n">
-        <v>2.10236287117004</v>
+        <v>2.1023633480072</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>2.84764504432678</v>
       </c>
       <c r="G844" t="n">
-        <v>2.11949253082275</v>
+        <v>2.11949229240417</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.85576701164246</v>
       </c>
       <c r="G845" t="n">
-        <v>2.12553715705872</v>
+        <v>2.12553739547729</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G849" t="n">
-        <v>2.09077525138855</v>
+        <v>2.09077477455139</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.71023797988892</v>
       </c>
       <c r="G852" t="n">
-        <v>2.01722097396851</v>
+        <v>2.01722073554993</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.68045496940613</v>
       </c>
       <c r="G853" t="n">
-        <v>1.99505305290222</v>
+        <v>1.9950532913208</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.63984203338623</v>
       </c>
       <c r="G854" t="n">
-        <v>1.96482527256012</v>
+        <v>1.96482503414154</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.61682796478271</v>
       </c>
       <c r="G856" t="n">
-        <v>1.94769585132599</v>
+        <v>1.94769561290741</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.67571711540222</v>
       </c>
       <c r="G857" t="n">
-        <v>1.99152684211731</v>
+        <v>1.99152660369873</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.68045496940613</v>
       </c>
       <c r="G858" t="n">
-        <v>1.99505305290222</v>
+        <v>1.9950532913208</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.45234489440918</v>
       </c>
       <c r="G860" t="n">
-        <v>1.82527148723602</v>
+        <v>1.82527184486389</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G861" t="n">
-        <v>1.78647887706757</v>
+        <v>1.78647875785828</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G862" t="n">
-        <v>1.76280069351196</v>
+        <v>1.76280045509338</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.3927800655365</v>
       </c>
       <c r="G863" t="n">
-        <v>1.78093779087067</v>
+        <v>1.78093755245209</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.32915306091309</v>
       </c>
       <c r="G864" t="n">
-        <v>1.73358035087585</v>
+        <v>1.73358047008514</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.29057002067566</v>
       </c>
       <c r="G868" t="n">
-        <v>1.70486307144165</v>
+        <v>1.70486330986023</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.27229404449463</v>
       </c>
       <c r="G869" t="n">
-        <v>1.69126045703888</v>
+        <v>1.69126057624817</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.24318909645081</v>
       </c>
       <c r="G872" t="n">
-        <v>1.66959798336029</v>
+        <v>1.66959762573242</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.30952310562134</v>
       </c>
       <c r="G874" t="n">
-        <v>1.71896994113922</v>
+        <v>1.71896982192993</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.33118295669556</v>
       </c>
       <c r="G875" t="n">
-        <v>1.73509132862091</v>
+        <v>1.7350914478302</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.33253693580627</v>
       </c>
       <c r="G877" t="n">
-        <v>1.73609912395477</v>
+        <v>1.73609900474548</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.34201288223267</v>
       </c>
       <c r="G879" t="n">
-        <v>1.74315214157104</v>
+        <v>1.74315178394318</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G880" t="n">
-        <v>1.78244888782501</v>
+        <v>1.78244864940643</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.47806692123413</v>
       </c>
       <c r="G883" t="n">
-        <v>1.8444162607193</v>
+        <v>1.84441649913788</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.45099210739136</v>
       </c>
       <c r="G884" t="n">
-        <v>1.82426476478577</v>
+        <v>1.82426452636719</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G885" t="n">
-        <v>1.78244888782501</v>
+        <v>1.78244864940643</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.44963788986206</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82325708866119</v>
+        <v>1.82325685024261</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.46385192871094</v>
       </c>
       <c r="G887" t="n">
-        <v>1.83383631706238</v>
+        <v>1.83383655548096</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.41240906715393</v>
       </c>
       <c r="G889" t="n">
-        <v>1.79554760456085</v>
+        <v>1.79554772377014</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.55793905258179</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90386545658112</v>
+        <v>1.90386521816254</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.63239598274231</v>
       </c>
       <c r="G892" t="n">
-        <v>1.95928275585175</v>
+        <v>1.9592832326889</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.63781094551086</v>
       </c>
       <c r="G893" t="n">
-        <v>1.96331346035004</v>
+        <v>1.96331322193146</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.61412000656128</v>
       </c>
       <c r="G894" t="n">
-        <v>1.94568026065826</v>
+        <v>1.94568014144897</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.59245991706848</v>
       </c>
       <c r="G895" t="n">
-        <v>1.92955911159515</v>
+        <v>1.92955887317657</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.5748610496521</v>
       </c>
       <c r="G899" t="n">
-        <v>1.91646003723145</v>
+        <v>1.91646027565002</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.61141300201416</v>
       </c>
       <c r="G900" t="n">
-        <v>1.94366526603699</v>
+        <v>1.94366550445557</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.56944608688354</v>
       </c>
       <c r="G901" t="n">
-        <v>1.91243016719818</v>
+        <v>1.91242969036102</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.59245991706848</v>
       </c>
       <c r="G902" t="n">
-        <v>1.92955911159515</v>
+        <v>1.92955887317657</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.53695607185364</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88824760913849</v>
+        <v>1.88824737071991</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.54507803916931</v>
       </c>
       <c r="G904" t="n">
-        <v>1.8942928314209</v>
+        <v>1.89429259300232</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.44692993164062</v>
       </c>
       <c r="G907" t="n">
-        <v>1.8212411403656</v>
+        <v>1.82124137878418</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.3880410194397</v>
       </c>
       <c r="G909" t="n">
-        <v>1.77741074562073</v>
+        <v>1.77741062641144</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.28041696548462</v>
       </c>
       <c r="G911" t="n">
-        <v>1.69730627536774</v>
+        <v>1.69730639457703</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.34133696556091</v>
       </c>
       <c r="G912" t="n">
-        <v>1.74264907836914</v>
+        <v>1.74264895915985</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.34066009521484</v>
       </c>
       <c r="G914" t="n">
-        <v>1.7421452999115</v>
+        <v>1.74214518070221</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.32915306091309</v>
       </c>
       <c r="G917" t="n">
-        <v>1.73358035087585</v>
+        <v>1.73358047008514</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.16602396965027</v>
       </c>
       <c r="G918" t="n">
-        <v>1.61216413974762</v>
+        <v>1.61216402053833</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.14436411857605</v>
       </c>
       <c r="G920" t="n">
-        <v>1.59604239463806</v>
+        <v>1.59604251384735</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.03876996040344</v>
       </c>
       <c r="G921" t="n">
-        <v>1.51744937896729</v>
+        <v>1.517449259758</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.07261395454407</v>
       </c>
       <c r="G925" t="n">
-        <v>1.54263937473297</v>
+        <v>1.54263925552368</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.08073711395264</v>
       </c>
       <c r="G926" t="n">
-        <v>1.54868543148041</v>
+        <v>1.54868531227112</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.18159198760986</v>
       </c>
       <c r="G932" t="n">
-        <v>1.62375128269196</v>
+        <v>1.62375104427338</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.18633008003235</v>
       </c>
       <c r="G933" t="n">
-        <v>1.62727773189545</v>
+        <v>1.62727785110474</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.22288203239441</v>
       </c>
       <c r="G934" t="n">
-        <v>1.65448331832886</v>
+        <v>1.65448319911957</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.25198793411255</v>
       </c>
       <c r="G936" t="n">
-        <v>1.67614650726318</v>
+        <v>1.67614662647247</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G938" t="n">
-        <v>1.74113702774048</v>
+        <v>1.74113750457764</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G939" t="n">
-        <v>1.76078522205353</v>
+        <v>1.76078546047211</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.34268999099731</v>
       </c>
       <c r="G940" t="n">
-        <v>1.74365615844727</v>
+        <v>1.7436558008194</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.43880796432495</v>
       </c>
       <c r="G942" t="n">
-        <v>1.81519639492035</v>
+        <v>1.81519627571106</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.45031499862671</v>
       </c>
       <c r="G943" t="n">
-        <v>1.82376110553741</v>
+        <v>1.82376050949097</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.37044191360474</v>
       </c>
       <c r="G944" t="n">
-        <v>1.76431155204773</v>
+        <v>1.76431179046631</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.48889708518982</v>
       </c>
       <c r="G946" t="n">
-        <v>1.85247755050659</v>
+        <v>1.85247731208801</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.44692993164062</v>
       </c>
       <c r="G947" t="n">
-        <v>1.8212411403656</v>
+        <v>1.82124137878418</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.41443991661072</v>
       </c>
       <c r="G948" t="n">
-        <v>1.79705893993378</v>
+        <v>1.79705917835236</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.35284399986267</v>
       </c>
       <c r="G950" t="n">
-        <v>1.75121343135834</v>
+        <v>1.75121355056763</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.36705803871155</v>
       </c>
       <c r="G951" t="n">
-        <v>1.76179301738739</v>
+        <v>1.7617928981781</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G953" t="n">
-        <v>1.78647887706757</v>
+        <v>1.78647875785828</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.39751791954041</v>
       </c>
       <c r="G954" t="n">
-        <v>1.78446424007416</v>
+        <v>1.78446400165558</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.37518095970154</v>
       </c>
       <c r="G956" t="n">
-        <v>1.76783907413483</v>
+        <v>1.76783895492554</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G958" t="n">
-        <v>1.76280069351196</v>
+        <v>1.76280045509338</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.37585806846619</v>
       </c>
       <c r="G961" t="n">
-        <v>1.76834261417389</v>
+        <v>1.76834285259247</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.48957395553589</v>
       </c>
       <c r="G963" t="n">
-        <v>1.85298097133636</v>
+        <v>1.85298120975494</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.75355792045593</v>
       </c>
       <c r="G973" t="n">
-        <v>2.04946351051331</v>
+        <v>2.04946327209473</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.70753002166748</v>
       </c>
       <c r="G977" t="n">
-        <v>2.0152051448822</v>
+        <v>2.01520490646362</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.82733798027039</v>
       </c>
       <c r="G979" t="n">
-        <v>2.10437750816345</v>
+        <v>2.10437774658203</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.85576701164246</v>
       </c>
       <c r="G982" t="n">
-        <v>2.12553715705872</v>
+        <v>2.12553739547729</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.90314888954163</v>
       </c>
       <c r="G983" t="n">
-        <v>2.16080331802368</v>
+        <v>2.16080355644226</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.9437620639801</v>
       </c>
       <c r="G985" t="n">
-        <v>2.19103169441223</v>
+        <v>2.19103145599365</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.93360900878906</v>
       </c>
       <c r="G986" t="n">
-        <v>2.18347477912903</v>
+        <v>2.18347454071045</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.0777850151062</v>
       </c>
       <c r="G989" t="n">
-        <v>2.29078459739685</v>
+        <v>2.29078483581543</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.11907505989075</v>
       </c>
       <c r="G990" t="n">
-        <v>2.32151675224304</v>
+        <v>2.32151651382446</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>3.10147595405579</v>
       </c>
       <c r="G991" t="n">
-        <v>2.30841779708862</v>
+        <v>2.30841755867004</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>3.02701902389526</v>
       </c>
       <c r="G992" t="n">
-        <v>2.25299954414368</v>
+        <v>2.2529993057251</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.03649497032166</v>
       </c>
       <c r="G994" t="n">
-        <v>2.26005268096924</v>
+        <v>2.26005244255066</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.97016000747681</v>
       </c>
       <c r="G996" t="n">
-        <v>2.21067953109741</v>
+        <v>2.21067976951599</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.91397905349731</v>
       </c>
       <c r="G998" t="n">
-        <v>2.16886401176453</v>
+        <v>2.16886425018311</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.93563890457153</v>
       </c>
       <c r="G999" t="n">
-        <v>2.18498587608337</v>
+        <v>2.18498563766479</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.97151398658752</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21168756484985</v>
+        <v>2.21168732643127</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.98031401634216</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.21823716163635</v>
+        <v>2.21823740005493</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.02566504478455</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.25199198722839</v>
+        <v>2.25199174880981</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.03649497032166</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.26005268096924</v>
+        <v>2.26005244255066</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.08658409118652</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.29733347892761</v>
+        <v>2.29733371734619</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.05680108070374</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.27516651153564</v>
+        <v>2.27516627311707</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.0527400970459</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.27214360237122</v>
+        <v>2.27214384078979</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.11027503013611</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.31496691703796</v>
+        <v>2.31496667861938</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.12719702720642</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.32756161689758</v>
+        <v>2.32756185531616</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.11366009712219</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.31748652458191</v>
+        <v>2.31748628616333</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.12381291389465</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.32504320144653</v>
+        <v>2.32504296302795</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.09606099128723</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.30438733100891</v>
+        <v>2.30438756942749</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.08793807029724</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.29834127426147</v>
+        <v>2.29834151268005</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.0933530330658</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.30237197875977</v>
+        <v>2.30237174034119</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.13261198997498</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.33159255981445</v>
+        <v>2.33159232139587</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.01821899414062</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.24644994735718</v>
+        <v>2.2464497089386</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.01889610290527</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.24695372581482</v>
+        <v>2.2469539642334</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.03378701210022</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.25803685188293</v>
+        <v>2.25803709030151</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.09077525138855</v>
+        <v>2.09077477455139</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.93090105056763</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.1814591884613</v>
+        <v>2.18145895004272</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.9627149105072</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.20513844490051</v>
+        <v>2.20513820648193</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.96000695228577</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.20312285423279</v>
+        <v>2.20312261581421</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.06898498535156</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.28423476219177</v>
+        <v>2.28423452377319</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.08658409118652</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.29733347892761</v>
+        <v>2.29733371734619</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.33965301513672</v>
+        <v>2.33965277671814</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.80296993255615</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.08624076843262</v>
+        <v>2.0862410068512</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.79349398612976</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.07918763160706</v>
+        <v>2.07918787002563</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.83884501457214</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.11294221878052</v>
+        <v>2.1129424571991</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.59652090072632</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.93258142471313</v>
+        <v>1.93258130550385</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.43610000610352</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.81318080425262</v>
+        <v>1.81318056583405</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>2.25063395500183</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.6751389503479</v>
+        <v>1.67513871192932</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.78697001934052</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.33003544807434</v>
+        <v>1.33003556728363</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.70032894611359</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.26554870605469</v>
+        <v>1.26554882526398</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.70439004898071</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.26857161521912</v>
+        <v>1.26857149600983</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.40182304382324</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.04337203502655</v>
+        <v>1.04337191581726</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.71589696407318</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.2771360874176</v>
+        <v>1.27713620662689</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.57916700839996</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.17536854743958</v>
+        <v>1.17536842823029</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.53719997406006</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.14413249492645</v>
+        <v>1.14413261413574</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.74297201633453</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.297287940979</v>
+        <v>1.29728782176971</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.98732697963715</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.47916042804718</v>
+        <v>1.47916054725647</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>2.00492596626282</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.49225950241089</v>
+        <v>1.49225926399231</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.96566700935364</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.46303904056549</v>
+        <v>1.46303915977478</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.83841300010681</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36832427978516</v>
+        <v>1.36832416057587</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.89527094364166</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.41064345836639</v>
+        <v>1.41064357757568</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.82555198669434</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.35875189304352</v>
+        <v>1.35875201225281</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.85195004940033</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.3783997297287</v>
+        <v>1.37839996814728</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.84450495243073</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.37285852432251</v>
+        <v>1.3728586435318</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.75380194187164</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.30534863471985</v>
+        <v>1.30534851551056</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.77072405815125</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.31794369220734</v>
+        <v>1.31794357299805</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.4992949962616</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.1159200668335</v>
+        <v>1.11591994762421</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.51621699333191</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.1285148859024</v>
+        <v>1.12851500511169</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.45055902004242</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.07964587211609</v>
+        <v>1.07964599132538</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.49726402759552</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.1144083738327</v>
+        <v>1.11440849304199</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.43499100208282</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.06805860996246</v>
+        <v>1.06805884838104</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.56833696365356</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.16730761528015</v>
+        <v>1.16730773448944</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.59338104724884</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.18594801425934</v>
+        <v>1.18594789505005</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.43499100208282</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.06805860996246</v>
+        <v>1.06805884838104</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.44717502593994</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.07712733745575</v>
+        <v>1.07712721824646</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.43092894554138</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.06503534317017</v>
+        <v>1.06503522396088</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.42145299911499</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.05798244476318</v>
+        <v>1.05798232555389</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.36324095726013</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.01465547084808</v>
+        <v>1.01465535163879</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.38490104675293</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.03077709674835</v>
+        <v>1.03077697753906</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.26170897483826</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.939085483551025</v>
+        <v>0.93908554315567</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.26509296894073</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.941604197025299</v>
+        <v>0.941604316234589</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.51621699333191</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.1285148859024</v>
+        <v>1.12851500511169</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.80118405818939</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.34061515331268</v>
+        <v>1.34061503410339</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.68611395359039</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.25496864318848</v>
+        <v>1.25496876239777</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.5784900188446</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.17486476898193</v>
+        <v>1.17486464977264</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.5568300485611</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.15874326229095</v>
+        <v>1.15874314308167</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.65903902053833</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.23481690883636</v>
+        <v>1.23481678962708</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.62587201595306</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.21013081073761</v>
+        <v>1.21013104915619</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.58119702339172</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.17687940597534</v>
+        <v>1.17687928676605</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.59744298458099</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.18897104263306</v>
+        <v>1.18897116184235</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.53584599494934</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.14312481880188</v>
+        <v>1.14312493801117</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.57375204563141</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.17133808135986</v>
+        <v>1.17133820056915</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.47086501121521</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.0947597026825</v>
+        <v>1.09475982189178</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.49726402759552</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.1144083738327</v>
+        <v>1.11440849304199</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.46815800666809</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.09274482727051</v>
+        <v>1.0927449464798</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.51689302921295</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.12901818752289</v>
+        <v>1.12901830673218</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.49997103214264</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.1164231300354</v>
+        <v>1.11642324924469</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.4539430141449</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.08216464519501</v>
+        <v>1.0821647644043</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.52704703807831</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.13657569885254</v>
+        <v>1.13657581806183</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.59744298458099</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.18897104263306</v>
+        <v>1.18897116184235</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.68679094314575</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.25547254085541</v>
+        <v>1.2554726600647</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.69694399833679</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.2630295753479</v>
+        <v>1.26302945613861</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.71928095817566</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.27965474128723</v>
+        <v>1.27965462207794</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.74161899089813</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.29628098011017</v>
+        <v>1.29628074169159</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.5723979473114</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.17033040523529</v>
+        <v>1.170330286026</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.57713603973389</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.17385685443878</v>
+        <v>1.17385673522949</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.52637004852295</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.13607180118561</v>
+        <v>1.1360719203949</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.4431129693985</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.07410395145416</v>
+        <v>1.07410383224487</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.4058849811554</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.04639506340027</v>
+        <v>1.04639518260956</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.46815800666809</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.09274482727051</v>
+        <v>1.0927449464798</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.49997103214264</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.1164231300354</v>
+        <v>1.11642324924469</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.58390498161316</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.17889487743378</v>
+        <v>1.17889499664307</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.60556495189667</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.19501626491547</v>
+        <v>1.19501614570618</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.58390498161316</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.17889487743378</v>
+        <v>1.17889499664307</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.57172095775604</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.16982650756836</v>
+        <v>1.16982638835907</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.58593595027924</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.18040633201599</v>
+        <v>1.18040657043457</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.54329204559326</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.14866673946381</v>
+        <v>1.1486668586731</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.58390498161316</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.17889487743378</v>
+        <v>1.17889499664307</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.58931994438171</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.1829252243042</v>
+        <v>1.18292534351349</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.61098003387451</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.19904685020447</v>
+        <v>1.19904673099518</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.55750596523285</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.15924608707428</v>
+        <v>1.15924620628357</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.51147794723511</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.12498772144318</v>
+        <v>1.12498784065247</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.43025195598602</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.06453156471252</v>
+        <v>1.06453144550323</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.48304903507233</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.10382807254791</v>
+        <v>1.10382831096649</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.47492694854736</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.09778308868408</v>
+        <v>1.09778296947479</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.36730194091797</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.01767802238464</v>
+        <v>1.01767814159393</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.31992101669312</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.98241263628006</v>
+        <v>0.98241251707077</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.34564197063446</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.00155663490295</v>
+        <v>1.00155651569366</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.3185670375824</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.981404781341553</v>
+        <v>0.981404900550842</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.28269195556641</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.954703211784363</v>
+        <v>0.954702973365784</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.884224116802216</v>
+        <v>0.88422417640686</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.19649994373322</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.89055073261261</v>
+        <v>0.890550673007965</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.11650002002716</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.831007063388824</v>
+        <v>0.83100700378418</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.20050001144409</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.893527984619141</v>
+        <v>0.893528044223785</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.18649995326996</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.883107662200928</v>
+        <v>0.883107841014862</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.20350003242493</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.895760715007782</v>
+        <v>0.895760893821716</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.19149994850159</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.886829257011414</v>
+        <v>0.886829316616058</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.03649997711182</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.771463334560394</v>
+        <v>0.771463394165039</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.01699995994568</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.756949543952942</v>
+        <v>0.756949484348297</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.785232782363892</v>
+        <v>0.785232841968536</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.805328786373138</v>
+        <v>0.805328845977783</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.08299994468689</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.806073069572449</v>
+        <v>0.806073009967804</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.19649994373322</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.89055073261261</v>
+        <v>0.890550673007965</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.18649995326996</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.883107662200928</v>
+        <v>0.883107841014862</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.896133005619049</v>
+        <v>0.896132946014404</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.48450005054474</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.10490810871124</v>
+        <v>1.10490822792053</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.12835359573364</v>
+        <v>1.12835347652435</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.51950001716614</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.1309586763382</v>
+        <v>1.13095855712891</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.52450001239777</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.13467991352081</v>
+        <v>1.13467979431152</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.12463188171387</v>
+        <v>1.12463200092316</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.09039449691772</v>
+        <v>1.09039437770844</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.10602450370789</v>
+        <v>1.1060243844986</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.09411597251892</v>
+        <v>1.09411573410034</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.4835000038147</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.10416376590729</v>
+        <v>1.10416400432587</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.4724999666214</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.09597647190094</v>
+        <v>1.09597671031952</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.46449995040894</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.09002220630646</v>
+        <v>1.09002232551575</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.47449994087219</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.09746527671814</v>
+        <v>1.09746515750885</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.12463188171387</v>
+        <v>1.12463200092316</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.47749996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.09969818592072</v>
+        <v>1.09969806671143</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.10155880451202</v>
+        <v>1.10155892372131</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.5</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.1164448261261</v>
+        <v>1.11644470691681</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.55250000953674</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.15552031993866</v>
+        <v>1.15552020072937</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.21320343017578</v>
+        <v>1.21320331096649</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.23999774456024</v>
+        <v>1.23999798297882</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.64549994468689</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.22473978996277</v>
+        <v>1.22473990917206</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.64450001716614</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.2239955663681</v>
+        <v>1.22399544715881</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.20650482177734</v>
+        <v>1.20650470256805</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.22734487056732</v>
+        <v>1.22734498977661</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.57050001621246</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.16891765594482</v>
+        <v>1.16891753673553</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.13430786132812</v>
+        <v>1.13430798053741</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.55850005149841</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.15998613834381</v>
+        <v>1.15998601913452</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.51950001716614</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.1309586763382</v>
+        <v>1.13095855712891</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.14100658893585</v>
+        <v>1.14100670814514</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.14919376373291</v>
+        <v>1.1491938829422</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.21320343017578</v>
+        <v>1.21320331096649</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.26381540298462</v>
+        <v>1.26381528377533</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.90950000286102</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42123413085938</v>
+        <v>1.42123436927795</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.86549997329712</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.38848507404327</v>
+        <v>1.38848519325256</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.38588011264801</v>
+        <v>1.3858802318573</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.40151023864746</v>
+        <v>1.40151035785675</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.85549998283386</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.38104212284088</v>
+        <v>1.38104200363159</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.86099994182587</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.38513576984406</v>
+        <v>1.38513588905334</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.86549997329712</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.38848507404327</v>
+        <v>1.38848519325256</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.38588011264801</v>
+        <v>1.3858802318573</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.86249995231628</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.38625228404999</v>
+        <v>1.3862521648407</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.37173855304718</v>
+        <v>1.37173843383789</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.37992548942566</v>
+        <v>1.37992560863495</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.47668421268463</v>
+        <v>1.47668409347534</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.45807695388794</v>
+        <v>1.45807683467865</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.44914543628693</v>
+        <v>1.44914531707764</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.52729630470276</v>
+        <v>1.52729642391205</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.51613175868988</v>
+        <v>1.51613187789917</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.41937339305878</v>
+        <v>1.4193731546402</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.41788470745087</v>
+        <v>1.41788482666016</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.93149995803833</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.43760871887207</v>
+        <v>1.43760883808136</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.42681646347046</v>
+        <v>1.42681634426117</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.41267478466034</v>
+        <v>1.41267454624176</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.89950001239777</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.41379129886627</v>
+        <v>1.41379117965698</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.41341924667358</v>
+        <v>1.413419008255</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.89950001239777</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.41379129886627</v>
+        <v>1.41379117965698</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.90349996089935</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.41676831245422</v>
+        <v>1.41676843166351</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.40076613426208</v>
+        <v>1.40076589584351</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.40895330905914</v>
+        <v>1.40895318984985</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.45212244987488</v>
+        <v>1.45212233066559</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.34345507621765</v>
+        <v>1.34345531463623</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.34568810462952</v>
+        <v>1.34568798542023</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.4096976518631</v>
+        <v>1.40969753265381</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.41267478466034</v>
+        <v>1.41267454624176</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.41937339305878</v>
+        <v>1.4193731546402</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.87450003623962</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.395183801651</v>
+        <v>1.39518392086029</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.438725233078</v>
+        <v>1.43872511386871</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.92349994182587</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.4316543340683</v>
+        <v>1.43165421485901</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.50050187110901</v>
+        <v>1.50050175189972</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.49231433868408</v>
+        <v>1.49231445789337</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>1.95850002765656</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.45770478248596</v>
+        <v>1.45770466327667</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.994500041008</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.48449945449829</v>
+        <v>1.484499335289</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.55703437328339</v>
+        <v>1.5570342540741</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.54716038703918</v>
+        <v>1.54716062545776</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.54032504558563</v>
+        <v>1.54032492637634</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.544881939888</v>
+        <v>1.54488170146942</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.55247724056244</v>
+        <v>1.55247712135315</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.5357677936554</v>
+        <v>1.53576767444611</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.04900002479553</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.55627477169037</v>
+        <v>1.55627501010895</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.55931293964386</v>
+        <v>1.55931305885315</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.03099989891052</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.54260325431824</v>
+        <v>1.54260337352753</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.52589392662048</v>
+        <v>1.52589380741119</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.45981466770172</v>
+        <v>1.45981478691101</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.45449793338776</v>
+        <v>1.45449805259705</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.88950002193451</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.43513000011444</v>
+        <v>1.43513011932373</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>1.84150004386902</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.39867258071899</v>
+        <v>1.39867269992828</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.40360951423645</v>
+        <v>1.40360975265503</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.36639261245728</v>
+        <v>1.36639273166656</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.34588539600372</v>
+        <v>1.34588527679443</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.29423749446869</v>
+        <v>1.2942373752594</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.55250000953674</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.17916882038116</v>
+        <v>1.17916858196259</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.20385336875916</v>
+        <v>1.20385348796844</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>1.61450004577637</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.22625958919525</v>
+        <v>1.22625946998596</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.24486815929413</v>
+        <v>1.24486804008484</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.62349998950958</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.23309516906738</v>
+        <v>1.23309528827667</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.3732283115387</v>
+        <v>1.37322819232941</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.82749998569489</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.38803923130035</v>
+        <v>1.38803911209106</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.37094974517822</v>
+        <v>1.37094986438751</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.36259496212006</v>
+        <v>1.36259508132935</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.83150005340576</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.39107739925385</v>
+        <v>1.39107728004456</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.81449997425079</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.37816536426544</v>
+        <v>1.37816524505615</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.81449997425079</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.37816536426544</v>
+        <v>1.37816524505615</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>1.83150005340576</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.39107739925385</v>
+        <v>1.39107728004456</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.38386166095734</v>
+        <v>1.38386178016663</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.78849995136261</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.35841751098633</v>
+        <v>1.35841763019562</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>1.78949999809265</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.35917711257935</v>
+        <v>1.35917699337006</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.90450000762939</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.44652307033539</v>
+        <v>1.4465229511261</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.4909553527832</v>
+        <v>1.49095547199249</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.54336309432983</v>
+        <v>1.54336297512054</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.52665328979492</v>
+        <v>1.52665317058563</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.03299999237061</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54412233829498</v>
+        <v>1.54412245750427</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.56994640827179</v>
+        <v>1.5699462890625</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.56462967395782</v>
+        <v>1.56462979316711</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.03099989891052</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.54260325431824</v>
+        <v>1.54260337352753</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.06299996376038</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.5669082403183</v>
+        <v>1.56690812110901</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.04900002479553</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.55627477169037</v>
+        <v>1.55627501010895</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.57830119132996</v>
+        <v>1.57830131053925</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.55551528930664</v>
+        <v>1.55551540851593</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55931293964386</v>
+        <v>1.55931305885315</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.5547559261322</v>
+        <v>1.55475580692291</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.88349997997284</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.4305727481842</v>
+        <v>1.43057286739349</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>1.91750001907349</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.4563969373703</v>
+        <v>1.45639681816101</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.43702876567841</v>
+        <v>1.43702864646912</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.45753622055054</v>
+        <v>1.45753610134125</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>1.90950000286102</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.45032060146332</v>
+        <v>1.45032072067261</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>1.92349994182587</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.46095407009125</v>
+        <v>1.46095395088196</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.45145988464355</v>
+        <v>1.45145964622498</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.46285271644592</v>
+        <v>1.46285283565521</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.40285003185272</v>
+        <v>1.40285015106201</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.36335456371307</v>
+        <v>1.36335444450378</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.27752792835236</v>
+        <v>1.27752780914307</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.73049998283386</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.31436491012573</v>
+        <v>1.31436502933502</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.30183267593384</v>
+        <v>1.30183255672455</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.28968024253845</v>
+        <v>1.28968012332916</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.32537806034088</v>
+        <v>1.32537817955017</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.34892344474792</v>
+        <v>1.34892356395721</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.7775000333786</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.35006284713745</v>
+        <v>1.35006272792816</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.81299996376038</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.37702608108521</v>
+        <v>1.37702596187592</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.38765943050385</v>
+        <v>1.38765954971313</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.38462114334106</v>
+        <v>1.38462126255035</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.43171203136444</v>
+        <v>1.43171215057373</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.4590550661087</v>
+        <v>1.45905518531799</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.90950000286102</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.45032060146332</v>
+        <v>1.45032072067261</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.90950000286102</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.45032060146332</v>
+        <v>1.45032072067261</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.45525741577148</v>
+        <v>1.45525753498077</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.92799997329712</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.46437180042267</v>
+        <v>1.46437191963196</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.47044813632965</v>
+        <v>1.47044801712036</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.47044813632965</v>
+        <v>1.47044801712036</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.45449793338776</v>
+        <v>1.45449805259705</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.42943358421326</v>
+        <v>1.42943346500397</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.85450005531311</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.40854644775391</v>
+        <v>1.4085465669632</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.46285271644592</v>
+        <v>1.46285283565521</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.50158870220184</v>
+        <v>1.50158858299255</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.5547559261322</v>
+        <v>1.55475580692291</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.55551528930664</v>
+        <v>1.55551540851593</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.53348898887634</v>
+        <v>1.53348910808563</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.37550687789917</v>
+        <v>1.37550711631775</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.40057134628296</v>
+        <v>1.40057146549225</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.36335456371307</v>
+        <v>1.36335444450378</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.66149997711182</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.26195728778839</v>
+        <v>1.26195740699768</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.25702035427094</v>
+        <v>1.25702047348022</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1.4025000333786</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.06523942947388</v>
+        <v>1.06523954868317</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.08308839797974</v>
+        <v>1.08308827877045</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.12106466293335</v>
+        <v>1.12106478214264</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.20005571842194</v>
+        <v>1.20005583763123</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.59049999713898</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.20803093910217</v>
+        <v>1.20803081989288</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.17802941799164</v>
+        <v>1.17802953720093</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.56149995326996</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.18600451946259</v>
+        <v>1.1860044002533</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>1.58949995040894</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.20727133750916</v>
+        <v>1.20727121829987</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.20005571842194</v>
+        <v>1.20005583763123</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.54050004482269</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.17005455493927</v>
+        <v>1.17005443572998</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.24638712406158</v>
+        <v>1.24638700485229</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.61749994754791</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.22853803634644</v>
+        <v>1.22853815555573</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>1.59350001811981</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.21030938625336</v>
+        <v>1.21030950546265</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.2023344039917</v>
+        <v>1.20233428478241</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.21904397010803</v>
+        <v>1.21904408931732</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>1.55550003051758</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.18144750595093</v>
+        <v>1.18144738674164</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>1.53149998188019</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.16321849822998</v>
+        <v>1.16321861743927</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>1.53349995613098</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.16473758220673</v>
+        <v>1.16473770141602</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>1.52149999141693</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.15562343597412</v>
+        <v>1.15562319755554</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.24638712406158</v>
+        <v>1.24638700485229</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.29119920730591</v>
+        <v>1.2911993265152</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.76549994945526</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.34094834327698</v>
+        <v>1.34094822406769</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.33449232578278</v>
+        <v>1.33449244499207</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.43073534965515</v>
+        <v>1.43073546886444</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>1.88450002670288</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.48225438594818</v>
+        <v>1.48225426673889</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>1.91649997234344</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.50742387771606</v>
+        <v>1.50742399692535</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.46534359455109</v>
+        <v>1.46534371376038</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G1637" t="n">
-        <v>1.52512145042419</v>
+        <v>1.5251213312149</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.34972059726715</v>
+        <v>1.34972071647644</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.65849995613098</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.30449390411377</v>
+        <v>1.30449402332306</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.19477021694183</v>
+        <v>1.19477009773254</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.11572194099426</v>
+        <v>1.11572182178497</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.18769109249115</v>
+        <v>1.18769121170044</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.10588991641998</v>
+        <v>1.10588979721069</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.29550004005432</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.01897633075714</v>
+        <v>1.01897621154785</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G1672" t="n">
-        <v>1.03588712215424</v>
+        <v>1.03588700294495</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.03824663162231</v>
+        <v>1.0382467508316</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>1.38699996471405</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.09094548225403</v>
+        <v>1.09094536304474</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.2466824054718</v>
+        <v>1.24668252468109</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.22151279449463</v>
+        <v>1.22151291370392</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.16409480571747</v>
+        <v>1.16409468650818</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.18375837802887</v>
+        <v>1.18375849723816</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.47749996185303</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.16212821006775</v>
+        <v>1.16212832927704</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.21758008003235</v>
+        <v>1.21757996082306</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.31275296211243</v>
+        <v>1.31275284290314</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>1.67550003528595</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.31786525249481</v>
+        <v>1.3178653717041</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.32612419128418</v>
+        <v>1.32612407207489</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.3646651506424</v>
+        <v>1.36466503143311</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.30882000923157</v>
+        <v>1.30881989002228</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>1.61150002479553</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.26752603054047</v>
+        <v>1.26752614974976</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>1.64849996566772</v>
       </c>
       <c r="G1721" t="n">
-        <v>1.29662847518921</v>
+        <v>1.29662835597992</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.25690770149231</v>
+        <v>1.2569078207016</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.59949994087219</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.25808727741241</v>
+        <v>1.2580873966217</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.78250002861023</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.40202629566193</v>
+        <v>1.40202617645264</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.44174695014954</v>
+        <v>1.44174706935883</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.49051320552826</v>
+        <v>1.49051308631897</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.89250004291534</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.48854672908783</v>
+        <v>1.48854684829712</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.4755687713623</v>
+        <v>1.47556865215302</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.90950000286102</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.50191819667816</v>
+        <v>1.50191807746887</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.50939047336578</v>
+        <v>1.50939035415649</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.95150005817413</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.5349532365799</v>
+        <v>1.53495335578918</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.53298687934875</v>
+        <v>1.53298699855804</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.92900002002716</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.51725602149963</v>
+        <v>1.51725590229034</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>1.9375</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.52394163608551</v>
+        <v>1.5239417552948</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.52826762199402</v>
+        <v>1.52826750278473</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.54478514194489</v>
+        <v>1.5447850227356</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.47871482372284</v>
+        <v>1.47871494293213</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>1.86549997329712</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.46730971336365</v>
+        <v>1.46730995178223</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.53298687934875</v>
+        <v>1.53298699855804</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.52197515964508</v>
+        <v>1.52197504043579</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.91849994659424</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.50899708271027</v>
+        <v>1.50899720191956</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.60220324993134</v>
+        <v>1.60220336914062</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.08299994468689</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.63838458061218</v>
+        <v>1.63838469982147</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.09299993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.64625012874603</v>
+        <v>1.64625024795532</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.65962147712708</v>
+        <v>1.65962159633636</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.66827368736267</v>
+        <v>1.66827356815338</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.72254550457001</v>
+        <v>1.72254574298859</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.77131187915802</v>
+        <v>1.77131164073944</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.30699992179871</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.8145717382431</v>
+        <v>1.81457197666168</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.84052813053131</v>
+        <v>1.84052789211273</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.8444607257843</v>
+        <v>1.84446096420288</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.04503154754639</v>
+        <v>2.04503130912781</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.57100009918213</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.02222156524658</v>
+        <v>2.022221326828</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.55299997329712</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.00806355476379</v>
+        <v>2.00806331634521</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.19604873657227</v>
+        <v>2.19604897499084</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.74699997901917</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.16065406799316</v>
+        <v>2.16065382957458</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.07649326324463</v>
+        <v>2.07649350166321</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.02851390838623</v>
+        <v>2.02851366996765</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.67899990081787</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.10716843605042</v>
+        <v>2.10716867446899</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.70099997520447</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.12447309494019</v>
+        <v>2.12447285652161</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>2.82699990272522</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.22357797622681</v>
+        <v>2.22357821464539</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.91525030136108</v>
+        <v>1.91525053977966</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.80592000484467</v>
+        <v>1.80591976642609</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.30100011825562</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.80985271930695</v>
+        <v>1.80985295772552</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.78468322753906</v>
+        <v>1.78468310832977</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.84524738788605</v>
+        <v>1.84524714946747</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.73827648162842</v>
+        <v>1.738276720047</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.75872695446014</v>
+        <v>1.75872707366943</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.76423287391663</v>
+        <v>1.76423275470734</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G1851" t="n">
-        <v>1.85940527915955</v>
+        <v>1.85940551757812</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.85625898838043</v>
+        <v>1.85625922679901</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.88614809513092</v>
+        <v>1.88614785671234</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.67899990081787</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.10716843605042</v>
+        <v>2.10716867446899</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.12840557098389</v>
+        <v>2.12840580940247</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.15908098220825</v>
+        <v>2.15908074378967</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.15042877197266</v>
+        <v>2.15042901039124</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.0859317779541</v>
+        <v>2.08593201637268</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.00413036346436</v>
+        <v>2.00413060188293</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.50699996948242</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.97188210487366</v>
+        <v>1.97188186645508</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.60700011253357</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.05053734779358</v>
+        <v>2.050537109375</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.07649326324463</v>
+        <v>2.07649350166321</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.14728283882141</v>
+        <v>2.14728307723999</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71099996566772</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.13233828544617</v>
+        <v>2.13233852386475</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.11896705627441</v>
+        <v>2.11896729469299</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>13.289999961853</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>3991583</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>13.460000038147</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>13.3179998397827</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>13.3240003585815</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>13.4460000991821</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>13.4460000991821</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
